--- a/Gicht_Fitnees_APP.xlsx
+++ b/Gicht_Fitnees_APP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\erne.dom\dfs\userdata\sem5647\Documents\Desktop\Gichttagebuch_APP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthias\Desktop\Fitness App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1519CD1-9380-4ECD-A7A5-7AE5B5F5CC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45ADEBDD-6FD2-4E1E-95F1-2E16E5D02121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Masterfile" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -3134,7 +3132,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3158,6 +3156,116 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -3206,261 +3314,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3615,6 +3468,22 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3628,12 +3497,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3681,6 +3546,22 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3694,12 +3575,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3747,6 +3624,22 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3760,12 +3653,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3813,6 +3702,40 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3857,6 +3780,7 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3876,6 +3800,80 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -9501,39 +9499,39 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:AF307">
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Datum" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="KG" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="KFA" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Skel.Musk" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="KCAL" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Prot" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Defizit/Überschuss" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="KG" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="KFA" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Skel.Musk" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="KCAL" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Prot" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Defizit/Überschuss" dataDxfId="25">
       <calculatedColumnFormula>Table_1[[#This Row],[KCAL]]-2200</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Früstück" dataDxfId="29"/>
-    <tableColumn id="42" xr3:uid="{AD8F3E03-B6EB-491A-A8AD-992F186710C1}" name="Frühstück-Ampel" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Frühstück-Notiz" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Mittagessen" dataDxfId="27"/>
-    <tableColumn id="43" xr3:uid="{72B2DB14-82FB-4433-9AEB-2CA5299094A0}" name="Mittagessen-Ampel" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Mittagessen-Notiz" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Abendessen" dataDxfId="25"/>
-    <tableColumn id="44" xr3:uid="{EE2E31CC-1E94-4545-8866-3D700E84CBF1}" name="Abendessen-Ampel" dataDxfId="9"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Abendessen-Notiz" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Snacks" dataDxfId="23"/>
-    <tableColumn id="45" xr3:uid="{6AFB462A-9E40-48CD-8A80-AAAFF3A133DC}" name="Snack-Ampel" dataDxfId="8"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Snacks-Notiz" dataDxfId="22"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Wasser/Soda/Zitrone" dataDxfId="21"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Red-Bull" dataDxfId="20"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Kaffee" dataDxfId="19"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Whey (Scoops)" dataDxfId="18"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Getränke-Sonstige" dataDxfId="17"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Schritte" dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Training (min)" dataDxfId="1"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Fahrrad (km)" dataDxfId="0"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Training-Sonstiges" dataDxfId="16"/>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Notiz11 Training" dataDxfId="15"/>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Subbs" dataDxfId="14"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Notiz12 Tageszusammenfassung" dataDxfId="13"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Gicht Status" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Früstück" dataDxfId="24"/>
+    <tableColumn id="42" xr3:uid="{AD8F3E03-B6EB-491A-A8AD-992F186710C1}" name="Frühstück-Ampel" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Frühstück-Notiz" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Mittagessen" dataDxfId="21"/>
+    <tableColumn id="43" xr3:uid="{72B2DB14-82FB-4433-9AEB-2CA5299094A0}" name="Mittagessen-Ampel" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Mittagessen-Notiz" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Abendessen" dataDxfId="18"/>
+    <tableColumn id="44" xr3:uid="{EE2E31CC-1E94-4545-8866-3D700E84CBF1}" name="Abendessen-Ampel" dataDxfId="17"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Abendessen-Notiz" dataDxfId="16"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Snacks" dataDxfId="15"/>
+    <tableColumn id="45" xr3:uid="{6AFB462A-9E40-48CD-8A80-AAAFF3A133DC}" name="Snack-Ampel" dataDxfId="14"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Snacks-Notiz" dataDxfId="13"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Wasser/Soda/Zitrone" dataDxfId="12"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Red-Bull" dataDxfId="11"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Kaffee" dataDxfId="10"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Whey (Scoops)" dataDxfId="9"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Getränke-Sonstige" dataDxfId="8"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Schritte" dataDxfId="7"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Training (min)" dataDxfId="6"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Fahrrad (km)" dataDxfId="5"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Training-Sonstiges" dataDxfId="4"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Notiz11 Training" dataDxfId="3"/>
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Subbs" dataDxfId="2"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Notiz12 Tageszusammenfassung" dataDxfId="1"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Gicht Status" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Masterfile-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9738,29 +9736,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="6" width="11.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
-    <col min="8" max="8" width="40.5703125" customWidth="1"/>
+    <col min="1" max="6" width="11.54296875" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="8" max="8" width="40.54296875" customWidth="1"/>
     <col min="9" max="11" width="19" customWidth="1"/>
-    <col min="12" max="14" width="18.140625" customWidth="1"/>
-    <col min="15" max="15" width="18.5703125" customWidth="1"/>
-    <col min="16" max="17" width="40.5703125" customWidth="1"/>
-    <col min="18" max="19" width="21.7109375" customWidth="1"/>
-    <col min="20" max="20" width="20.140625" customWidth="1"/>
-    <col min="21" max="22" width="5.5703125" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" customWidth="1"/>
-    <col min="24" max="24" width="40.5703125" customWidth="1"/>
-    <col min="25" max="25" width="8.42578125" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" customWidth="1"/>
-    <col min="27" max="27" width="12.85546875" customWidth="1"/>
-    <col min="28" max="28" width="26.85546875" customWidth="1"/>
-    <col min="29" max="29" width="40.5703125" customWidth="1"/>
-    <col min="30" max="30" width="27.140625" customWidth="1"/>
-    <col min="31" max="31" width="47.7109375" customWidth="1"/>
-    <col min="32" max="32" width="17.42578125" customWidth="1"/>
-    <col min="33" max="34" width="40.5703125" customWidth="1"/>
+    <col min="12" max="14" width="18.1796875" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" customWidth="1"/>
+    <col min="16" max="17" width="40.54296875" customWidth="1"/>
+    <col min="18" max="19" width="21.7265625" customWidth="1"/>
+    <col min="20" max="20" width="20.1796875" customWidth="1"/>
+    <col min="21" max="22" width="5.54296875" customWidth="1"/>
+    <col min="23" max="23" width="12.1796875" customWidth="1"/>
+    <col min="24" max="24" width="40.54296875" customWidth="1"/>
+    <col min="25" max="25" width="8.453125" customWidth="1"/>
+    <col min="26" max="26" width="11.1796875" customWidth="1"/>
+    <col min="27" max="27" width="12.81640625" customWidth="1"/>
+    <col min="28" max="28" width="26.81640625" customWidth="1"/>
+    <col min="29" max="29" width="40.54296875" customWidth="1"/>
+    <col min="30" max="30" width="27.1796875" customWidth="1"/>
+    <col min="31" max="31" width="47.7265625" customWidth="1"/>
+    <col min="32" max="32" width="17.453125" customWidth="1"/>
+    <col min="33" max="34" width="40.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="14.25" customHeight="1">
@@ -15493,7 +15491,9 @@
       <c r="C94" s="22">
         <v>12.9</v>
       </c>
-      <c r="D94" s="22"/>
+      <c r="D94" s="22">
+        <v>34.549999999999997</v>
+      </c>
       <c r="E94" s="23">
         <v>2825</v>
       </c>
@@ -15570,7 +15570,9 @@
       <c r="C95" s="28">
         <v>12.6</v>
       </c>
-      <c r="D95" s="28"/>
+      <c r="D95" s="28">
+        <v>34.549999999999997</v>
+      </c>
       <c r="E95" s="26">
         <v>1997</v>
       </c>
@@ -15655,7 +15657,9 @@
       <c r="C96" s="22">
         <v>12.5</v>
       </c>
-      <c r="D96" s="22"/>
+      <c r="D96" s="22">
+        <v>34.54</v>
+      </c>
       <c r="E96" s="23">
         <v>2151</v>
       </c>
@@ -15732,7 +15736,9 @@
       <c r="C97" s="28">
         <v>13.1</v>
       </c>
-      <c r="D97" s="28"/>
+      <c r="D97" s="28">
+        <v>34.51</v>
+      </c>
       <c r="E97" s="26">
         <v>2089</v>
       </c>
@@ -15815,7 +15821,9 @@
       <c r="C98" s="22">
         <v>13.3</v>
       </c>
-      <c r="D98" s="22"/>
+      <c r="D98" s="22">
+        <v>34.369999999999997</v>
+      </c>
       <c r="E98" s="23">
         <v>1727</v>
       </c>
@@ -15898,7 +15906,9 @@
       <c r="C99" s="28">
         <v>13.3</v>
       </c>
-      <c r="D99" s="28"/>
+      <c r="D99" s="28">
+        <v>34.29</v>
+      </c>
       <c r="E99" s="26">
         <v>2940</v>
       </c>
@@ -15979,7 +15989,9 @@
       <c r="C100" s="22">
         <v>13.6</v>
       </c>
-      <c r="D100" s="22"/>
+      <c r="D100" s="22">
+        <v>34.69</v>
+      </c>
       <c r="E100" s="23">
         <v>1950</v>
       </c>
@@ -16060,7 +16072,9 @@
       <c r="C101" s="28">
         <v>13.3</v>
       </c>
-      <c r="D101" s="28"/>
+      <c r="D101" s="28">
+        <v>34.51</v>
+      </c>
       <c r="E101" s="26">
         <v>1594</v>
       </c>
@@ -16145,7 +16159,9 @@
       <c r="C102" s="22">
         <v>12.9</v>
       </c>
-      <c r="D102" s="22"/>
+      <c r="D102" s="22">
+        <v>34.200000000000003</v>
+      </c>
       <c r="E102" s="23">
         <v>1823</v>
       </c>
@@ -16230,7 +16246,9 @@
       <c r="C103" s="28">
         <v>13.4</v>
       </c>
-      <c r="D103" s="28"/>
+      <c r="D103" s="28">
+        <v>34.17</v>
+      </c>
       <c r="E103" s="26">
         <v>2137</v>
       </c>
@@ -16317,7 +16335,9 @@
       <c r="C104" s="22">
         <v>13</v>
       </c>
-      <c r="D104" s="22"/>
+      <c r="D104" s="22">
+        <v>34.51</v>
+      </c>
       <c r="E104" s="23">
         <v>2180</v>
       </c>
@@ -16404,7 +16424,9 @@
       <c r="C105" s="28">
         <v>13.1</v>
       </c>
-      <c r="D105" s="28"/>
+      <c r="D105" s="28">
+        <v>34.24</v>
+      </c>
       <c r="E105" s="26">
         <v>2493</v>
       </c>
@@ -16485,7 +16507,9 @@
       <c r="C106" s="22">
         <v>13</v>
       </c>
-      <c r="D106" s="22"/>
+      <c r="D106" s="22">
+        <v>34.229999999999997</v>
+      </c>
       <c r="E106" s="23">
         <v>2125</v>
       </c>
@@ -16564,7 +16588,9 @@
       <c r="C107" s="28">
         <v>13.9</v>
       </c>
-      <c r="D107" s="28"/>
+      <c r="D107" s="28">
+        <v>34.4</v>
+      </c>
       <c r="E107" s="26">
         <v>2100</v>
       </c>
@@ -16655,7 +16681,9 @@
       <c r="C108" s="22">
         <v>13.5</v>
       </c>
-      <c r="D108" s="22"/>
+      <c r="D108" s="22">
+        <v>34.659999999999997</v>
+      </c>
       <c r="E108" s="23">
         <v>2500</v>
       </c>
@@ -16736,7 +16764,9 @@
       <c r="C109" s="28">
         <v>13.3</v>
       </c>
-      <c r="D109" s="28"/>
+      <c r="D109" s="28">
+        <v>34.39</v>
+      </c>
       <c r="E109" s="26">
         <v>2527</v>
       </c>
@@ -16827,7 +16857,9 @@
       <c r="C110" s="22">
         <v>13.3</v>
       </c>
-      <c r="D110" s="22"/>
+      <c r="D110" s="22">
+        <v>34.61</v>
+      </c>
       <c r="E110" s="23">
         <v>2162</v>
       </c>
@@ -16914,7 +16946,9 @@
       <c r="C111" s="28">
         <v>13.3</v>
       </c>
-      <c r="D111" s="28"/>
+      <c r="D111" s="28">
+        <v>34.659999999999997</v>
+      </c>
       <c r="E111" s="26">
         <v>1795</v>
       </c>
@@ -17001,7 +17035,9 @@
       <c r="C112" s="22">
         <v>13.3</v>
       </c>
-      <c r="D112" s="22"/>
+      <c r="D112" s="22">
+        <v>34.81</v>
+      </c>
       <c r="E112" s="23">
         <v>1893</v>
       </c>
@@ -17086,7 +17122,9 @@
       <c r="C113" s="28">
         <v>12.9</v>
       </c>
-      <c r="D113" s="28"/>
+      <c r="D113" s="28">
+        <v>34.450000000000003</v>
+      </c>
       <c r="E113" s="26">
         <v>2650</v>
       </c>
@@ -17173,7 +17211,9 @@
       <c r="C114" s="28">
         <v>13.3</v>
       </c>
-      <c r="D114" s="28"/>
+      <c r="D114" s="28">
+        <v>34.86</v>
+      </c>
       <c r="E114" s="23">
         <v>2220</v>
       </c>
@@ -17264,7 +17304,9 @@
       <c r="C115" s="28">
         <v>12.8</v>
       </c>
-      <c r="D115" s="28"/>
+      <c r="D115" s="28">
+        <v>34.97</v>
+      </c>
       <c r="E115" s="26">
         <v>2755</v>
       </c>
@@ -17351,7 +17393,9 @@
       <c r="C116" s="28">
         <v>13.2</v>
       </c>
-      <c r="D116" s="28"/>
+      <c r="D116" s="28">
+        <v>34.56</v>
+      </c>
       <c r="E116" s="26">
         <v>2270</v>
       </c>
@@ -17438,7 +17482,9 @@
       <c r="C117" s="28">
         <v>13.2</v>
       </c>
-      <c r="D117" s="28"/>
+      <c r="D117" s="28">
+        <v>34.44</v>
+      </c>
       <c r="E117" s="26">
         <v>1785</v>
       </c>
@@ -17531,7 +17577,9 @@
       <c r="C118" s="28">
         <v>13.4</v>
       </c>
-      <c r="D118" s="28"/>
+      <c r="D118" s="28">
+        <v>34.61</v>
+      </c>
       <c r="E118" s="26">
         <v>1650</v>
       </c>
@@ -17626,7 +17674,9 @@
       <c r="C119" s="28">
         <v>12.7</v>
       </c>
-      <c r="D119" s="28"/>
+      <c r="D119" s="28">
+        <v>34.450000000000003</v>
+      </c>
       <c r="E119" s="26">
         <v>2050</v>
       </c>
@@ -17719,7 +17769,9 @@
       <c r="C120" s="28">
         <v>13.1</v>
       </c>
-      <c r="D120" s="28"/>
+      <c r="D120" s="28">
+        <v>34.51</v>
+      </c>
       <c r="E120" s="26">
         <v>1950</v>
       </c>
@@ -17808,7 +17860,9 @@
       <c r="C121" s="28">
         <v>12.5</v>
       </c>
-      <c r="D121" s="28"/>
+      <c r="D121" s="28">
+        <v>34.47</v>
+      </c>
       <c r="E121" s="26">
         <v>1640</v>
       </c>
@@ -17899,7 +17953,9 @@
       <c r="C122" s="28">
         <v>13.3</v>
       </c>
-      <c r="D122" s="28"/>
+      <c r="D122" s="28">
+        <v>34.25</v>
+      </c>
       <c r="E122" s="26"/>
       <c r="F122" s="49">
         <v>100</v>
@@ -17988,7 +18044,9 @@
       <c r="C123" s="28">
         <v>13.3</v>
       </c>
-      <c r="D123" s="28"/>
+      <c r="D123" s="28">
+        <v>34.46</v>
+      </c>
       <c r="E123" s="26">
         <v>1840</v>
       </c>
@@ -18079,7 +18137,9 @@
       <c r="C124" s="28">
         <v>13.4</v>
       </c>
-      <c r="D124" s="28"/>
+      <c r="D124" s="28">
+        <v>34.71</v>
+      </c>
       <c r="E124" s="26">
         <v>2095</v>
       </c>
@@ -18172,7 +18232,9 @@
       <c r="C125" s="28">
         <v>13.4</v>
       </c>
-      <c r="D125" s="28"/>
+      <c r="D125" s="28">
+        <v>34.47</v>
+      </c>
       <c r="E125" s="26">
         <v>2250</v>
       </c>
@@ -18265,7 +18327,9 @@
       <c r="C126" s="28">
         <v>13.5</v>
       </c>
-      <c r="D126" s="28"/>
+      <c r="D126" s="28">
+        <v>34.700000000000003</v>
+      </c>
       <c r="E126" s="26">
         <v>1625</v>
       </c>
@@ -18360,7 +18424,9 @@
       <c r="C127" s="28">
         <v>12.6</v>
       </c>
-      <c r="D127" s="28"/>
+      <c r="D127" s="28">
+        <v>34.409999999999997</v>
+      </c>
       <c r="E127" s="26">
         <v>1686</v>
       </c>
@@ -18453,7 +18519,9 @@
       <c r="C128" s="28">
         <v>12.7</v>
       </c>
-      <c r="D128" s="28"/>
+      <c r="D128" s="28">
+        <v>34.29</v>
+      </c>
       <c r="E128" s="26">
         <v>2430</v>
       </c>
@@ -18544,7 +18612,9 @@
       <c r="C129" s="28">
         <v>13</v>
       </c>
-      <c r="D129" s="28"/>
+      <c r="D129" s="28">
+        <v>34.01</v>
+      </c>
       <c r="E129" s="26">
         <v>2038</v>
       </c>
@@ -18633,7 +18703,9 @@
       <c r="C130" s="28">
         <v>13.3</v>
       </c>
-      <c r="D130" s="28"/>
+      <c r="D130" s="28">
+        <v>34.97</v>
+      </c>
       <c r="E130" s="26">
         <v>2337</v>
       </c>
@@ -18724,7 +18796,9 @@
       <c r="C131" s="28">
         <v>12.9</v>
       </c>
-      <c r="D131" s="28"/>
+      <c r="D131" s="28">
+        <v>33.659999999999997</v>
+      </c>
       <c r="E131" s="26">
         <v>2020</v>
       </c>
@@ -18811,7 +18885,9 @@
       <c r="C132" s="28">
         <v>13</v>
       </c>
-      <c r="D132" s="28"/>
+      <c r="D132" s="28">
+        <v>34.04</v>
+      </c>
       <c r="E132" s="26">
         <v>2028</v>
       </c>
@@ -18908,7 +18984,9 @@
       <c r="C133" s="28">
         <v>12.6</v>
       </c>
-      <c r="D133" s="28"/>
+      <c r="D133" s="28">
+        <v>34.61</v>
+      </c>
       <c r="E133" s="26">
         <v>2058</v>
       </c>
@@ -18995,7 +19073,9 @@
       <c r="C134" s="28">
         <v>12.9</v>
       </c>
-      <c r="D134" s="28"/>
+      <c r="D134" s="28">
+        <v>34.42</v>
+      </c>
       <c r="E134" s="26">
         <v>3408</v>
       </c>
@@ -19088,7 +19168,9 @@
       <c r="C135" s="28">
         <v>13.3</v>
       </c>
-      <c r="D135" s="28"/>
+      <c r="D135" s="28">
+        <v>34.28</v>
+      </c>
       <c r="E135" s="26">
         <v>2020</v>
       </c>
@@ -19179,7 +19261,9 @@
       <c r="C136" s="28">
         <v>12.7</v>
       </c>
-      <c r="D136" s="28"/>
+      <c r="D136" s="28">
+        <v>34.159999999999997</v>
+      </c>
       <c r="E136" s="26">
         <v>1975</v>
       </c>
@@ -19272,7 +19356,9 @@
       <c r="C137" s="28">
         <v>12.9</v>
       </c>
-      <c r="D137" s="28"/>
+      <c r="D137" s="28">
+        <v>34.159999999999997</v>
+      </c>
       <c r="E137" s="26">
         <v>1381</v>
       </c>
@@ -19361,7 +19447,9 @@
       <c r="C138" s="28">
         <v>12.7</v>
       </c>
-      <c r="D138" s="28"/>
+      <c r="D138" s="28">
+        <v>34.4</v>
+      </c>
       <c r="E138" s="26">
         <v>1500</v>
       </c>
@@ -19452,7 +19540,9 @@
       <c r="C139" s="28">
         <v>12.7</v>
       </c>
-      <c r="D139" s="28"/>
+      <c r="D139" s="28">
+        <v>34.6</v>
+      </c>
       <c r="E139" s="26">
         <v>1872</v>
       </c>
@@ -19541,7 +19631,9 @@
       <c r="C140" s="28">
         <v>12.6</v>
       </c>
-      <c r="D140" s="28"/>
+      <c r="D140" s="28">
+        <v>33.85</v>
+      </c>
       <c r="E140" s="26">
         <v>2484</v>
       </c>
@@ -19626,7 +19718,9 @@
       <c r="C141" s="28">
         <v>12.7</v>
       </c>
-      <c r="D141" s="28"/>
+      <c r="D141" s="28">
+        <v>33.93</v>
+      </c>
       <c r="E141" s="26">
         <v>2545</v>
       </c>
@@ -19707,7 +19801,9 @@
       <c r="C142" s="28">
         <v>12.9</v>
       </c>
-      <c r="D142" s="28"/>
+      <c r="D142" s="28">
+        <v>34.299999999999997</v>
+      </c>
       <c r="E142" s="26">
         <v>2537</v>
       </c>
@@ -19802,7 +19898,9 @@
       <c r="C143" s="28">
         <v>13.3</v>
       </c>
-      <c r="D143" s="28"/>
+      <c r="D143" s="28">
+        <v>34.42</v>
+      </c>
       <c r="E143" s="26">
         <v>1952</v>
       </c>
@@ -19889,7 +19987,9 @@
       <c r="C144" s="28">
         <v>13.7</v>
       </c>
-      <c r="D144" s="28"/>
+      <c r="D144" s="28">
+        <v>34.25</v>
+      </c>
       <c r="E144" s="26">
         <v>2073</v>
       </c>
@@ -19980,7 +20080,9 @@
       <c r="C145" s="28">
         <v>13</v>
       </c>
-      <c r="D145" s="28"/>
+      <c r="D145" s="28">
+        <v>34.26</v>
+      </c>
       <c r="E145" s="26">
         <v>2071</v>
       </c>
@@ -20069,7 +20171,9 @@
       <c r="C146" s="28">
         <v>13.3</v>
       </c>
-      <c r="D146" s="28"/>
+      <c r="D146" s="28">
+        <v>34.020000000000003</v>
+      </c>
       <c r="E146" s="26">
         <v>2349</v>
       </c>
@@ -20162,7 +20266,9 @@
       <c r="C147" s="28">
         <v>13.6</v>
       </c>
-      <c r="D147" s="28"/>
+      <c r="D147" s="28">
+        <v>34.1</v>
+      </c>
       <c r="E147" s="26">
         <v>2105</v>
       </c>
@@ -51965,12 +52071,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="26" width="10.7109375" customWidth="1"/>
+    <col min="1" max="26" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -51978,7 +52084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.5">
       <c r="A2" s="2">
         <f>Masterfile!A2</f>
         <v>46082</v>
@@ -51988,7 +52094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="14.5">
       <c r="A3" s="2">
         <f>Masterfile!A3</f>
         <v>46083</v>
@@ -51998,7 +52104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="14.5">
       <c r="A4" s="2">
         <f>Masterfile!A4</f>
         <v>46084</v>
@@ -52008,7 +52114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="14.5">
       <c r="A5" s="2">
         <f>Masterfile!A5</f>
         <v>46085</v>
@@ -52018,7 +52124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="14.5">
       <c r="A6" s="2">
         <f>Masterfile!A6</f>
         <v>46086</v>
@@ -52028,7 +52134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="14.5">
       <c r="A7" s="2">
         <f>Masterfile!A7</f>
         <v>46087</v>
@@ -52038,7 +52144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="14.5">
       <c r="A8" s="2">
         <f>Masterfile!A8</f>
         <v>46088</v>
@@ -52048,7 +52154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="14.5">
       <c r="A9" s="2">
         <f>Masterfile!A9</f>
         <v>46089</v>
@@ -52058,7 +52164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="14.5">
       <c r="A10" s="2">
         <f>Masterfile!A10</f>
         <v>46090</v>
@@ -52068,7 +52174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="14.5">
       <c r="A11" s="2">
         <f>Masterfile!A11</f>
         <v>46091</v>
@@ -52078,7 +52184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" ht="14.5">
       <c r="A12" s="2">
         <f>Masterfile!A12</f>
         <v>46092</v>
@@ -52088,7 +52194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="14.5">
       <c r="A13" s="2">
         <f>Masterfile!A13</f>
         <v>46093</v>
@@ -52098,7 +52204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="14.5">
       <c r="A14" s="2">
         <f>Masterfile!A14</f>
         <v>46094</v>
@@ -52108,7 +52214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="14.5">
       <c r="A15" s="2">
         <f>Masterfile!A15</f>
         <v>46095</v>
@@ -52118,7 +52224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="14.5">
       <c r="A16" s="2">
         <f>Masterfile!A16</f>
         <v>46096</v>
@@ -52128,7 +52234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" ht="14.5">
       <c r="A17" s="2">
         <f>Masterfile!A17</f>
         <v>46097</v>
@@ -52138,7 +52244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" ht="14.5">
       <c r="A18" s="2">
         <f>Masterfile!A18</f>
         <v>46098</v>
@@ -52148,7 +52254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" ht="14.5">
       <c r="A19" s="2">
         <f>Masterfile!A19</f>
         <v>46099</v>
@@ -52158,7 +52264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" ht="14.5">
       <c r="A20" s="2">
         <f>Masterfile!A20</f>
         <v>46100</v>

--- a/Gicht_Fitnees_APP.xlsx
+++ b/Gicht_Fitnees_APP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matthias\Desktop\Fitness App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EF9D9E-C3E7-4DD8-B08B-C722AE25A6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D36F6D-F6E7-4769-89D4-D6BA852B9E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="1680" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Masterfile" sheetId="1" r:id="rId1"/>
@@ -65,36 +65,24 @@
     <t>Defizit/Überschuss</t>
   </si>
   <si>
-    <t>Früstück</t>
-  </si>
-  <si>
     <t>Frühstück-Ampel</t>
   </si>
   <si>
     <t>Frühstück-Notiz</t>
   </si>
   <si>
-    <t>Mittagessen</t>
-  </si>
-  <si>
     <t>Mittagessen-Ampel</t>
   </si>
   <si>
     <t>Mittagessen-Notiz</t>
   </si>
   <si>
-    <t>Abendessen</t>
-  </si>
-  <si>
     <t>Abendessen-Ampel</t>
   </si>
   <si>
     <t>Abendessen-Notiz</t>
   </si>
   <si>
-    <t>Snacks</t>
-  </si>
-  <si>
     <t>Snack-Ampel</t>
   </si>
   <si>
@@ -2892,6 +2880,18 @@
   </si>
   <si>
     <t>Geburststag voll ausgekostet</t>
+  </si>
+  <si>
+    <t>Früstück-Titel</t>
+  </si>
+  <si>
+    <t>Mittagessen-Titel</t>
+  </si>
+  <si>
+    <t>Abendessen-Titel</t>
+  </si>
+  <si>
+    <t>Snack Titel</t>
   </si>
 </sst>
 </file>
@@ -3093,7 +3093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3233,30 +3233,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3281,13 +3262,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Masterfile-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -8895,16 +8892,16 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="KCAL"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Prot"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Defizit/Überschuss"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Früstück"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Früstück-Titel"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Frühstück-Ampel"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Frühstück-Notiz"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Mittagessen"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Mittagessen-Titel"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Mittagessen-Ampel"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Mittagessen-Notiz"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Abendessen"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Abendessen-Titel"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Abendessen-Ampel"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Abendessen-Notiz"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Snacks"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Snack Titel"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Snack-Ampel"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Snacks-Notiz"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Wasser/Soda/Zitrone"/>
@@ -9172,79 +9169,79 @@
         <v>7</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="7" t="s">
+        <v>948</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="O1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="P1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="Q1" s="11" t="s">
+        <v>950</v>
+      </c>
+      <c r="R1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="S1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="T1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="U1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="V1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="W1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="X1" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="X1" s="13" t="s">
-        <v>24</v>
       </c>
       <c r="Y1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="Z1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="14" t="s">
+      <c r="AE1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="14" t="s">
+      <c r="AF1" s="17" t="s">
         <v>27</v>
-      </c>
-      <c r="AC1" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="17" t="s">
-        <v>31</v>
       </c>
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
@@ -10132,7 +10129,7 @@
         <v>-2200</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I23" s="36"/>
       <c r="J23" s="35"/>
@@ -11144,31 +11141,31 @@
         <v>-2200</v>
       </c>
       <c r="H47" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J47" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I47" s="25" t="s">
+      <c r="M47" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="J47" s="23" t="s">
+      <c r="N47" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="K47" s="23" t="s">
+      <c r="O47" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P47" s="25" t="s">
         <v>36</v>
-      </c>
-      <c r="L47" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M47" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="N47" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="O47" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P47" s="25" t="s">
-        <v>40</v>
       </c>
       <c r="Q47" s="25"/>
       <c r="R47" s="25"/>
@@ -11182,7 +11179,7 @@
       </c>
       <c r="W47" s="25"/>
       <c r="X47" s="25" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Y47" s="26"/>
       <c r="Z47" s="27"/>
@@ -11190,7 +11187,7 @@
       <c r="AB47" s="25"/>
       <c r="AC47" s="25"/>
       <c r="AD47" s="25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE47" s="23"/>
       <c r="AF47" s="25" t="str">
@@ -11214,31 +11211,31 @@
         <v>-2200</v>
       </c>
       <c r="H48" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I48" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J48" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="K48" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="L48" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M48" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N48" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="I48" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J48" s="23" t="s">
+      <c r="O48" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P48" s="25" t="s">
         <v>44</v>
-      </c>
-      <c r="K48" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="L48" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N48" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="O48" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P48" s="25" t="s">
-        <v>48</v>
       </c>
       <c r="Q48" s="25"/>
       <c r="R48" s="25"/>
@@ -11254,7 +11251,7 @@
       </c>
       <c r="W48" s="25"/>
       <c r="X48" s="25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Y48" s="26"/>
       <c r="Z48" s="27"/>
@@ -11262,10 +11259,10 @@
       <c r="AB48" s="25"/>
       <c r="AC48" s="25"/>
       <c r="AD48" s="25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE48" s="23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF48" s="25" t="str">
         <f t="shared" ref="AF48:AF111" si="0">IF( ((I48="Rot")*2 + (L48="Rot")*2 + (O48="Rot")*2 + (R48="Rot")*2 + (I48="Gelb") + (L48="Gelb") + (O48="Gelb") + (R48="Gelb")) &gt;= 4, "Rot", IF( ((I48="Rot")*2 + (L48="Rot")*2 + (O48="Rot")*2 + (R48="Rot")*2 + (I48="Gelb") + (L48="Gelb") + (O48="Gelb") + (R48="Gelb")) &gt;= 2, "Gelb", "Grün" ) )</f>
@@ -11294,40 +11291,40 @@
         <v>535</v>
       </c>
       <c r="H49" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J49" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="K49" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="I49" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49" s="23" t="s">
+      <c r="N49" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K49" s="23" t="s">
+      <c r="O49" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P49" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="L49" s="25" t="s">
+      <c r="Q49" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="M49" s="23" t="s">
+      <c r="R49" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S49" s="38" t="s">
         <v>55</v>
-      </c>
-      <c r="N49" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="O49" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P49" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q49" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="R49" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S49" s="38" t="s">
-        <v>59</v>
       </c>
       <c r="T49" s="25">
         <v>2.5</v>
@@ -11336,7 +11333,7 @@
       <c r="V49" s="25"/>
       <c r="W49" s="25"/>
       <c r="X49" s="25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Y49" s="26">
         <v>5127</v>
@@ -11347,7 +11344,7 @@
       <c r="AC49" s="25"/>
       <c r="AD49" s="25"/>
       <c r="AE49" s="23" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="AF49" s="25" t="str">
         <f t="shared" si="0"/>
@@ -11374,31 +11371,31 @@
         <v>842</v>
       </c>
       <c r="H50" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="I50" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J50" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="K50" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="L50" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I50" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50" s="23" t="s">
+      <c r="O50" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P50" s="25" t="s">
         <v>63</v>
-      </c>
-      <c r="K50" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="L50" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M50" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="N50" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="O50" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P50" s="25" t="s">
-        <v>67</v>
       </c>
       <c r="Q50" s="25"/>
       <c r="R50" s="25"/>
@@ -11412,7 +11409,7 @@
       </c>
       <c r="W50" s="25"/>
       <c r="X50" s="25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="Y50" s="26">
         <v>8902</v>
@@ -11425,7 +11422,7 @@
       <c r="AC50" s="25"/>
       <c r="AD50" s="25"/>
       <c r="AE50" s="23" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AF50" s="25" t="str">
         <f t="shared" si="0"/>
@@ -11454,31 +11451,31 @@
         <v>229</v>
       </c>
       <c r="H51" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I51" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="K51" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="L51" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="N51" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="I51" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J51" s="23" t="s">
+      <c r="O51" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P51" s="25" t="s">
         <v>71</v>
-      </c>
-      <c r="K51" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="L51" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M51" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="N51" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="O51" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P51" s="25" t="s">
-        <v>75</v>
       </c>
       <c r="Q51" s="25"/>
       <c r="R51" s="25"/>
@@ -11490,7 +11487,7 @@
       <c r="V51" s="25"/>
       <c r="W51" s="25"/>
       <c r="X51" s="25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="Y51" s="26">
         <v>2824</v>
@@ -11500,7 +11497,7 @@
       <c r="AB51" s="25"/>
       <c r="AC51" s="25"/>
       <c r="AD51" s="25" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AE51" s="23"/>
       <c r="AF51" s="25" t="str">
@@ -11528,31 +11525,31 @@
         <v>-141</v>
       </c>
       <c r="H52" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="I52" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J52" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="K52" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L52" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="N52" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="I52" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="J52" s="23" t="s">
+      <c r="O52" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P52" s="25" t="s">
         <v>78</v>
-      </c>
-      <c r="K52" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="L52" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M52" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="N52" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="O52" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P52" s="25" t="s">
-        <v>82</v>
       </c>
       <c r="Q52" s="25"/>
       <c r="R52" s="25"/>
@@ -11576,7 +11573,7 @@
       <c r="AB52" s="25"/>
       <c r="AC52" s="25"/>
       <c r="AD52" s="25" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AE52" s="23"/>
       <c r="AF52" s="25" t="str">
@@ -11604,31 +11601,31 @@
         <v>-230</v>
       </c>
       <c r="H53" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J53" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="K53" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="L53" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="N53" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="I53" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J53" s="23" t="s">
+      <c r="O53" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P53" s="25" t="s">
         <v>85</v>
-      </c>
-      <c r="K53" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="L53" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M53" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="N53" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="O53" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P53" s="25" t="s">
-        <v>89</v>
       </c>
       <c r="Q53" s="25"/>
       <c r="R53" s="25"/>
@@ -11654,7 +11651,7 @@
       <c r="AB53" s="25"/>
       <c r="AC53" s="25"/>
       <c r="AD53" s="25" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AE53" s="23"/>
       <c r="AF53" s="25" t="str">
@@ -11682,40 +11679,40 @@
         <v>-80</v>
       </c>
       <c r="H54" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="I54" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J54" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="K54" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="L54" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="N54" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="I54" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J54" s="23" t="s">
+      <c r="O54" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P54" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="K54" s="23" t="s">
+      <c r="Q54" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="L54" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M54" s="23" t="s">
+      <c r="R54" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S54" s="25" t="s">
         <v>93</v>
-      </c>
-      <c r="N54" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="O54" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P54" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q54" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="R54" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S54" s="25" t="s">
-        <v>97</v>
       </c>
       <c r="T54" s="25">
         <v>2.25</v>
@@ -11766,31 +11763,31 @@
         <v>-77</v>
       </c>
       <c r="H55" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J55" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="K55" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L55" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M55" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="N55" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="I55" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J55" s="23" t="s">
+      <c r="O55" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P55" s="25" t="s">
         <v>99</v>
-      </c>
-      <c r="K55" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="L55" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M55" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="N55" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="O55" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P55" s="25" t="s">
-        <v>103</v>
       </c>
       <c r="Q55" s="25"/>
       <c r="R55" s="25"/>
@@ -11844,31 +11841,31 @@
         <v>-580</v>
       </c>
       <c r="H56" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="I56" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J56" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="K56" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="L56" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="N56" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O56" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P56" s="25" t="s">
         <v>104</v>
-      </c>
-      <c r="I56" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J56" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="K56" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="L56" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M56" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="N56" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O56" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P56" s="25" t="s">
-        <v>108</v>
       </c>
       <c r="Q56" s="25"/>
       <c r="R56" s="25"/>
@@ -11892,7 +11889,7 @@
       <c r="AB56" s="25"/>
       <c r="AC56" s="25"/>
       <c r="AD56" s="25" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AE56" s="23"/>
       <c r="AF56" s="25" t="str">
@@ -11926,40 +11923,40 @@
         <v>-320</v>
       </c>
       <c r="H57" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="I57" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J57" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="K57" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="L57" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="N57" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="I57" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J57" s="23" t="s">
+      <c r="O57" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P57" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="K57" s="23" t="s">
+      <c r="Q57" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="L57" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M57" s="23" t="s">
+      <c r="R57" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S57" s="25" t="s">
         <v>113</v>
-      </c>
-      <c r="N57" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="O57" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P57" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q57" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="R57" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S57" s="25" t="s">
-        <v>117</v>
       </c>
       <c r="T57" s="25">
         <v>2.5</v>
@@ -11972,7 +11969,7 @@
       </c>
       <c r="W57" s="25"/>
       <c r="X57" s="25" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Y57" s="26">
         <v>8204</v>
@@ -11982,7 +11979,7 @@
       <c r="AB57" s="25"/>
       <c r="AC57" s="25"/>
       <c r="AD57" s="25" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AE57" s="23"/>
       <c r="AF57" s="25" t="str">
@@ -12016,31 +12013,31 @@
         <v>-110</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I58" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J58" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="K58" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="L58" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="N58" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="O58" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P58" s="25" t="s">
         <v>120</v>
-      </c>
-      <c r="K58" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="L58" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M58" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="N58" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="O58" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P58" s="25" t="s">
-        <v>124</v>
       </c>
       <c r="Q58" s="25"/>
       <c r="R58" s="25"/>
@@ -12062,7 +12059,7 @@
       <c r="AB58" s="25"/>
       <c r="AC58" s="25"/>
       <c r="AD58" s="25" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AE58" s="23"/>
       <c r="AF58" s="25" t="str">
@@ -12096,31 +12093,31 @@
         <v>-423</v>
       </c>
       <c r="H59" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I59" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J59" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="K59" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="L59" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="N59" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="I59" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J59" s="23" t="s">
+      <c r="O59" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P59" s="25" t="s">
         <v>127</v>
-      </c>
-      <c r="K59" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="L59" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M59" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="N59" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="O59" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P59" s="25" t="s">
-        <v>131</v>
       </c>
       <c r="Q59" s="25"/>
       <c r="R59" s="25"/>
@@ -12142,11 +12139,11 @@
       <c r="Z59" s="27"/>
       <c r="AA59" s="28"/>
       <c r="AB59" s="25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AC59" s="25"/>
       <c r="AD59" s="25" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="AE59" s="23"/>
       <c r="AF59" s="25" t="str">
@@ -12180,31 +12177,31 @@
         <v>-114</v>
       </c>
       <c r="H60" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="I60" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J60" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="K60" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="L60" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M60" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="N60" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="I60" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J60" s="23" t="s">
+      <c r="O60" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P60" s="25" t="s">
         <v>135</v>
-      </c>
-      <c r="K60" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="L60" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M60" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="N60" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="O60" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P60" s="25" t="s">
-        <v>139</v>
       </c>
       <c r="Q60" s="25"/>
       <c r="R60" s="25"/>
@@ -12226,11 +12223,11 @@
       <c r="Z60" s="27"/>
       <c r="AA60" s="28"/>
       <c r="AB60" s="25" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AC60" s="25"/>
       <c r="AD60" s="25" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AE60" s="23"/>
       <c r="AF60" s="25" t="str">
@@ -12264,31 +12261,31 @@
         <v>-410</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J61" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="K61" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="L61" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="N61" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="O61" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P61" s="25" t="s">
         <v>142</v>
-      </c>
-      <c r="K61" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="L61" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M61" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="N61" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="O61" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P61" s="25" t="s">
-        <v>146</v>
       </c>
       <c r="Q61" s="25"/>
       <c r="R61" s="25"/>
@@ -12310,11 +12307,11 @@
       <c r="Z61" s="27"/>
       <c r="AA61" s="28"/>
       <c r="AB61" s="25" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AC61" s="25"/>
       <c r="AD61" s="25" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AE61" s="23"/>
       <c r="AF61" s="25" t="str">
@@ -12348,31 +12345,31 @@
         <v>-625</v>
       </c>
       <c r="H62" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="I62" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J62" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="K62" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="L62" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="N62" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="I62" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J62" s="23" t="s">
+      <c r="O62" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P62" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="K62" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="L62" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M62" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="N62" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="O62" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P62" s="25" t="s">
-        <v>154</v>
       </c>
       <c r="Q62" s="25"/>
       <c r="R62" s="25"/>
@@ -12394,11 +12391,11 @@
       <c r="Z62" s="27"/>
       <c r="AA62" s="28"/>
       <c r="AB62" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AC62" s="25"/>
       <c r="AD62" s="25" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="AE62" s="23"/>
       <c r="AF62" s="25" t="str">
@@ -12432,40 +12429,40 @@
         <v>-389</v>
       </c>
       <c r="H63" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="I63" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J63" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="K63" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="L63" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="N63" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="I63" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J63" s="23" t="s">
+      <c r="O63" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P63" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="K63" s="23" t="s">
+      <c r="Q63" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="L63" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M63" s="23" t="s">
+      <c r="R63" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S63" s="25" t="s">
         <v>159</v>
-      </c>
-      <c r="N63" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="O63" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P63" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q63" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="R63" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S63" s="25" t="s">
-        <v>163</v>
       </c>
       <c r="T63" s="25">
         <v>5</v>
@@ -12478,7 +12475,7 @@
       </c>
       <c r="W63" s="25"/>
       <c r="X63" s="25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="Y63" s="26">
         <v>10437</v>
@@ -12488,14 +12485,14 @@
         <v>14.7</v>
       </c>
       <c r="AB63" s="25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AC63" s="25"/>
       <c r="AD63" s="25" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AE63" s="23" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AF63" s="25" t="str">
         <f t="shared" si="0"/>
@@ -12528,40 +12525,40 @@
         <v>-348</v>
       </c>
       <c r="H64" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="I64" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J64" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="K64" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="L64" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="N64" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="I64" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J64" s="23" t="s">
+      <c r="O64" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P64" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="K64" s="23" t="s">
+      <c r="Q64" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="L64" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M64" s="23" t="s">
+      <c r="R64" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S64" s="25" t="s">
         <v>170</v>
-      </c>
-      <c r="N64" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="O64" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P64" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q64" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="R64" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S64" s="25" t="s">
-        <v>174</v>
       </c>
       <c r="T64" s="25">
         <v>5.5</v>
@@ -12578,11 +12575,11 @@
       <c r="Z64" s="27"/>
       <c r="AA64" s="28"/>
       <c r="AB64" s="25" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AC64" s="25"/>
       <c r="AD64" s="25" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AE64" s="23"/>
       <c r="AF64" s="25" t="str">
@@ -12616,40 +12613,40 @@
         <v>750</v>
       </c>
       <c r="H65" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="I65" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J65" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="K65" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="L65" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="N65" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="I65" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J65" s="23" t="s">
+      <c r="O65" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P65" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="K65" s="23" t="s">
+      <c r="Q65" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="L65" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M65" s="23" t="s">
+      <c r="R65" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S65" s="25" t="s">
         <v>180</v>
-      </c>
-      <c r="N65" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="O65" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P65" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q65" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="R65" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S65" s="25" t="s">
-        <v>184</v>
       </c>
       <c r="T65" s="25">
         <v>4</v>
@@ -12660,7 +12657,7 @@
       </c>
       <c r="W65" s="25"/>
       <c r="X65" s="25" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Y65" s="26">
         <v>4852</v>
@@ -12670,7 +12667,7 @@
       <c r="AB65" s="25"/>
       <c r="AC65" s="25"/>
       <c r="AD65" s="25" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AE65" s="23"/>
       <c r="AF65" s="25" t="str">
@@ -12704,31 +12701,31 @@
         <v>-374</v>
       </c>
       <c r="H66" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="I66" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J66" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="K66" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="L66" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="N66" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="I66" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J66" s="23" t="s">
+      <c r="O66" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P66" s="25" t="s">
         <v>188</v>
-      </c>
-      <c r="K66" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="L66" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M66" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="N66" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="O66" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P66" s="25" t="s">
-        <v>192</v>
       </c>
       <c r="Q66" s="25"/>
       <c r="R66" s="25"/>
@@ -12752,11 +12749,11 @@
       </c>
       <c r="AA66" s="28"/>
       <c r="AB66" s="25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AC66" s="25"/>
       <c r="AD66" s="25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AE66" s="23"/>
       <c r="AF66" s="25" t="str">
@@ -12790,40 +12787,40 @@
         <v>-921</v>
       </c>
       <c r="H67" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J67" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="K67" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="L67" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="N67" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="O67" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P67" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="K67" s="23" t="s">
+      <c r="Q67" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="L67" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M67" s="23" t="s">
+      <c r="R67" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S67" s="25" t="s">
         <v>196</v>
-      </c>
-      <c r="N67" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="O67" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P67" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q67" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="R67" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S67" s="25" t="s">
-        <v>200</v>
       </c>
       <c r="T67" s="25">
         <v>5</v>
@@ -12838,7 +12835,7 @@
         <v>3</v>
       </c>
       <c r="X67" s="25" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="Y67" s="26">
         <v>14728</v>
@@ -12846,11 +12843,11 @@
       <c r="Z67" s="27"/>
       <c r="AA67" s="28"/>
       <c r="AB67" s="25" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AC67" s="25"/>
       <c r="AD67" s="25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AE67" s="23"/>
       <c r="AF67" s="25" t="str">
@@ -12884,31 +12881,31 @@
         <v>-133</v>
       </c>
       <c r="H68" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="I68" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J68" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="K68" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="L68" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="N68" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="I68" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J68" s="23" t="s">
+      <c r="O68" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P68" s="25" t="s">
         <v>204</v>
-      </c>
-      <c r="K68" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="L68" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M68" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="N68" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="O68" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P68" s="25" t="s">
-        <v>208</v>
       </c>
       <c r="Q68" s="25"/>
       <c r="R68" s="25"/>
@@ -12964,40 +12961,40 @@
         <v>-467</v>
       </c>
       <c r="H69" s="23" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I69" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J69" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="K69" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="L69" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="N69" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="O69" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P69" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="K69" s="23" t="s">
+      <c r="Q69" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="L69" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M69" s="23" t="s">
+      <c r="R69" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S69" s="25" t="s">
         <v>211</v>
-      </c>
-      <c r="N69" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="O69" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P69" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q69" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="R69" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S69" s="25" t="s">
-        <v>215</v>
       </c>
       <c r="T69" s="25">
         <v>5</v>
@@ -13018,7 +13015,7 @@
       <c r="AB69" s="25"/>
       <c r="AC69" s="25"/>
       <c r="AD69" s="25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AE69" s="23"/>
       <c r="AF69" s="25" t="str">
@@ -13052,35 +13049,35 @@
         <v>-1126</v>
       </c>
       <c r="H70" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="I70" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J70" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K70" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="L70" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="N70" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="I70" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J70" s="23" t="s">
+      <c r="O70" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P70" s="25" t="s">
         <v>217</v>
-      </c>
-      <c r="K70" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="L70" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M70" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="N70" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="O70" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P70" s="25" t="s">
-        <v>221</v>
       </c>
       <c r="Q70" s="25"/>
       <c r="R70" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S70" s="25"/>
       <c r="T70" s="25">
@@ -13102,11 +13099,11 @@
       </c>
       <c r="AA70" s="28"/>
       <c r="AB70" s="25" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AC70" s="25"/>
       <c r="AD70" s="25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AE70" s="23"/>
       <c r="AF70" s="25" t="str">
@@ -13140,40 +13137,40 @@
         <v>1925</v>
       </c>
       <c r="H71" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I71" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J71" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="K71" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="L71" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="N71" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="O71" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P71" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="K71" s="23" t="s">
+      <c r="Q71" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="L71" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M71" s="23" t="s">
+      <c r="R71" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S71" s="25" t="s">
         <v>225</v>
-      </c>
-      <c r="N71" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="O71" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P71" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q71" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="R71" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S71" s="25" t="s">
-        <v>229</v>
       </c>
       <c r="T71" s="25">
         <v>3.3</v>
@@ -13184,7 +13181,7 @@
       </c>
       <c r="W71" s="25"/>
       <c r="X71" s="25" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="Y71" s="26">
         <v>5570</v>
@@ -13194,7 +13191,7 @@
       <c r="AB71" s="25"/>
       <c r="AC71" s="25"/>
       <c r="AD71" s="25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AE71" s="23"/>
       <c r="AF71" s="25" t="str">
@@ -13228,40 +13225,40 @@
         <v>-121</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I72" s="25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J72" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="K72" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="L72" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="N72" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O72" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P72" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q72" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="K72" s="23" t="s">
+      <c r="R72" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S72" s="25" t="s">
         <v>232</v>
-      </c>
-      <c r="L72" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M72" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="N72" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O72" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P72" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q72" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="R72" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S72" s="25" t="s">
-        <v>236</v>
       </c>
       <c r="T72" s="25">
         <v>3.5</v>
@@ -13272,7 +13269,7 @@
       </c>
       <c r="W72" s="25"/>
       <c r="X72" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y72" s="26">
         <v>7446</v>
@@ -13282,7 +13279,7 @@
       <c r="AB72" s="25"/>
       <c r="AC72" s="25"/>
       <c r="AD72" s="25" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AE72" s="23"/>
       <c r="AF72" s="25" t="str">
@@ -13316,40 +13313,40 @@
         <v>-234</v>
       </c>
       <c r="H73" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="I73" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J73" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="K73" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="L73" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="N73" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="I73" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J73" s="23" t="s">
+      <c r="O73" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P73" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="K73" s="23" t="s">
+      <c r="Q73" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="L73" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M73" s="23" t="s">
+      <c r="R73" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S73" s="25" t="s">
         <v>241</v>
-      </c>
-      <c r="N73" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="O73" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P73" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q73" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="R73" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S73" s="25" t="s">
-        <v>245</v>
       </c>
       <c r="T73" s="25">
         <v>3.5</v>
@@ -13362,7 +13359,7 @@
       </c>
       <c r="W73" s="25"/>
       <c r="X73" s="25" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Y73" s="26">
         <v>7824</v>
@@ -13372,7 +13369,7 @@
       <c r="AB73" s="25"/>
       <c r="AC73" s="25"/>
       <c r="AD73" s="25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AE73" s="23"/>
       <c r="AF73" s="25" t="str">
@@ -13406,31 +13403,31 @@
         <v>-368</v>
       </c>
       <c r="H74" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="I74" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J74" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="K74" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="L74" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M74" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="N74" s="23" t="s">
         <v>247</v>
       </c>
-      <c r="I74" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J74" s="23" t="s">
+      <c r="O74" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P74" s="25" t="s">
         <v>248</v>
-      </c>
-      <c r="K74" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="L74" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M74" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="N74" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="O74" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P74" s="25" t="s">
-        <v>252</v>
       </c>
       <c r="Q74" s="25"/>
       <c r="R74" s="25"/>
@@ -13444,7 +13441,7 @@
       </c>
       <c r="W74" s="25"/>
       <c r="X74" s="25" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Y74" s="26">
         <v>2889</v>
@@ -13454,10 +13451,10 @@
       <c r="AB74" s="25"/>
       <c r="AC74" s="25"/>
       <c r="AD74" s="25" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AE74" s="23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AF74" s="25" t="str">
         <f t="shared" si="0"/>
@@ -13484,40 +13481,40 @@
         <v>-300</v>
       </c>
       <c r="H75" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="I75" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J75" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="K75" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="L75" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="N75" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="I75" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J75" s="23" t="s">
+      <c r="O75" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P75" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="K75" s="23" t="s">
+      <c r="Q75" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="L75" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M75" s="23" t="s">
+      <c r="R75" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S75" s="25" t="s">
         <v>258</v>
-      </c>
-      <c r="N75" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="O75" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P75" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q75" s="25" t="s">
-        <v>261</v>
-      </c>
-      <c r="R75" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S75" s="25" t="s">
-        <v>262</v>
       </c>
       <c r="T75" s="25">
         <v>3.5</v>
@@ -13536,10 +13533,10 @@
       <c r="AB75" s="25"/>
       <c r="AC75" s="25"/>
       <c r="AD75" s="25" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AE75" s="23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AF75" s="25" t="str">
         <f t="shared" si="0"/>
@@ -13572,40 +13569,40 @@
         <v>-946</v>
       </c>
       <c r="H76" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="I76" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J76" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="K76" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L76" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M76" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N76" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="O76" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="I76" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J76" s="23" t="s">
+      <c r="Q76" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="K76" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L76" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M76" s="23" t="s">
+      <c r="R76" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S76" s="38" t="s">
         <v>266</v>
-      </c>
-      <c r="N76" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="O76" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P76" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q76" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="R76" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S76" s="38" t="s">
-        <v>270</v>
       </c>
       <c r="T76" s="25">
         <v>4.5</v>
@@ -13616,7 +13613,7 @@
       </c>
       <c r="W76" s="25"/>
       <c r="X76" s="25" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Y76" s="26">
         <v>418</v>
@@ -13626,10 +13623,10 @@
       <c r="AB76" s="25"/>
       <c r="AC76" s="25"/>
       <c r="AD76" s="25" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AE76" s="23" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AF76" s="25" t="str">
         <f t="shared" si="0"/>
@@ -13662,40 +13659,40 @@
         <v>-799</v>
       </c>
       <c r="H77" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="I77" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J77" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="K77" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="L77" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M77" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="N77" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O77" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P77" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="I77" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J77" s="23" t="s">
+      <c r="Q77" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="K77" s="23" t="s">
+      <c r="R77" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S77" s="25" t="s">
         <v>273</v>
-      </c>
-      <c r="L77" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M77" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="N77" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O77" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P77" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q77" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="R77" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S77" s="25" t="s">
-        <v>277</v>
       </c>
       <c r="T77" s="25">
         <v>3.5</v>
@@ -13706,7 +13703,7 @@
       </c>
       <c r="W77" s="25"/>
       <c r="X77" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y77" s="26">
         <v>5783</v>
@@ -13716,7 +13713,7 @@
       <c r="AB77" s="25"/>
       <c r="AC77" s="25"/>
       <c r="AD77" s="25" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AE77" s="23"/>
       <c r="AF77" s="25" t="str">
@@ -13750,40 +13747,40 @@
         <v>373</v>
       </c>
       <c r="H78" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="I78" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J78" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="K78" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="L78" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M78" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="N78" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="I78" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J78" s="23" t="s">
+      <c r="O78" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P78" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="K78" s="23" t="s">
+      <c r="Q78" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="L78" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M78" s="23" t="s">
+      <c r="R78" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S78" s="25" t="s">
         <v>281</v>
-      </c>
-      <c r="N78" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="O78" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P78" s="25" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q78" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="R78" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S78" s="25" t="s">
-        <v>285</v>
       </c>
       <c r="T78" s="25">
         <v>3.5</v>
@@ -13794,7 +13791,7 @@
       </c>
       <c r="W78" s="25"/>
       <c r="X78" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y78" s="26">
         <v>3021</v>
@@ -13804,7 +13801,7 @@
       <c r="AB78" s="25"/>
       <c r="AC78" s="25"/>
       <c r="AD78" s="25" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AE78" s="23"/>
       <c r="AF78" s="25" t="str">
@@ -13838,40 +13835,40 @@
         <v>-31</v>
       </c>
       <c r="H79" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="I79" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J79" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="K79" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="L79" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="N79" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="I79" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J79" s="23" t="s">
+      <c r="O79" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P79" s="25" t="s">
         <v>287</v>
       </c>
-      <c r="K79" s="23" t="s">
+      <c r="Q79" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="L79" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M79" s="23" t="s">
+      <c r="R79" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S79" s="25" t="s">
         <v>289</v>
-      </c>
-      <c r="N79" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="O79" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P79" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q79" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="R79" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S79" s="25" t="s">
-        <v>293</v>
       </c>
       <c r="T79" s="25">
         <v>1.75</v>
@@ -13884,7 +13881,7 @@
         <v>3</v>
       </c>
       <c r="X79" s="25" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Y79" s="26">
         <v>4477</v>
@@ -13894,7 +13891,7 @@
       <c r="AB79" s="25"/>
       <c r="AC79" s="25"/>
       <c r="AD79" s="25" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AE79" s="23"/>
       <c r="AF79" s="25" t="str">
@@ -13928,40 +13925,40 @@
         <v>1298</v>
       </c>
       <c r="H80" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I80" s="25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J80" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="K80" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="L80" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="N80" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="O80" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P80" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="K80" s="23" t="s">
+      <c r="Q80" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="L80" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M80" s="23" t="s">
+      <c r="R80" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S80" s="25" t="s">
         <v>297</v>
-      </c>
-      <c r="N80" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="O80" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P80" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q80" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="R80" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S80" s="25" t="s">
-        <v>301</v>
       </c>
       <c r="T80" s="25">
         <v>3.75</v>
@@ -13982,7 +13979,7 @@
       <c r="AB80" s="25"/>
       <c r="AC80" s="25"/>
       <c r="AD80" s="25" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AE80" s="23"/>
       <c r="AF80" s="25" t="str">
@@ -14010,40 +14007,40 @@
         <v>1100</v>
       </c>
       <c r="H81" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="I81" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J81" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="K81" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="L81" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="N81" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="I81" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="J81" s="23" t="s">
+      <c r="O81" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P81" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="K81" s="23" t="s">
+      <c r="Q81" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="L81" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M81" s="23" t="s">
+      <c r="R81" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S81" s="25" t="s">
         <v>305</v>
-      </c>
-      <c r="N81" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="O81" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P81" s="25" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q81" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="R81" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S81" s="25" t="s">
-        <v>309</v>
       </c>
       <c r="T81" s="25">
         <v>3.3</v>
@@ -14058,7 +14055,7 @@
         <v>3</v>
       </c>
       <c r="X81" s="25" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="Y81" s="26">
         <v>5547</v>
@@ -14094,36 +14091,36 @@
         <v>1583</v>
       </c>
       <c r="H82" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="I82" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J82" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="K82" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="L82" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M82" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="N82" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="I82" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="J82" s="23" t="s">
+      <c r="O82" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P82" s="25" t="s">
         <v>312</v>
-      </c>
-      <c r="K82" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="L82" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M82" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="N82" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="O82" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P82" s="25" t="s">
-        <v>316</v>
       </c>
       <c r="Q82" s="25"/>
       <c r="R82" s="25"/>
       <c r="S82" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T82" s="25">
         <v>1.1000000000000001</v>
@@ -14138,7 +14135,7 @@
         <v>3</v>
       </c>
       <c r="X82" s="25" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="Y82" s="26">
         <v>5525</v>
@@ -14149,7 +14146,7 @@
       <c r="AC82" s="25"/>
       <c r="AD82" s="25"/>
       <c r="AE82" s="23" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AF82" s="25" t="str">
         <f t="shared" si="0"/>
@@ -14172,36 +14169,36 @@
         <v>-2200</v>
       </c>
       <c r="H83" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I83" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J83" s="23" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="K83" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L83" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M83" s="23" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="N83" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O83" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P83" s="25" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="Q83" s="25"/>
       <c r="R83" s="25"/>
       <c r="S83" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T83" s="25"/>
       <c r="U83" s="25"/>
@@ -14248,40 +14245,40 @@
         <v>-500</v>
       </c>
       <c r="H84" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I84" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J84" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="K84" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L84" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M84" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N84" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="O84" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P84" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q84" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="R84" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S84" s="25" t="s">
         <v>322</v>
-      </c>
-      <c r="K84" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L84" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M84" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="N84" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="O84" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P84" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q84" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="R84" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S84" s="25" t="s">
-        <v>326</v>
       </c>
       <c r="T84" s="25">
         <v>2</v>
@@ -14292,7 +14289,7 @@
       </c>
       <c r="W84" s="25"/>
       <c r="X84" s="25" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="Y84" s="26">
         <v>8879</v>
@@ -14334,40 +14331,40 @@
         <v>-629</v>
       </c>
       <c r="H85" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I85" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J85" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="K85" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="L85" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M85" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="N85" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="O85" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P85" s="25" t="s">
         <v>328</v>
       </c>
-      <c r="K85" s="23" t="s">
+      <c r="Q85" s="25" t="s">
         <v>329</v>
       </c>
-      <c r="L85" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M85" s="23" t="s">
+      <c r="R85" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S85" s="25" t="s">
         <v>330</v>
-      </c>
-      <c r="N85" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="O85" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P85" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q85" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="R85" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S85" s="25" t="s">
-        <v>334</v>
       </c>
       <c r="T85" s="25">
         <v>0.5</v>
@@ -14380,7 +14377,7 @@
       </c>
       <c r="W85" s="25"/>
       <c r="X85" s="25" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="Y85" s="26">
         <v>6159</v>
@@ -14422,31 +14419,31 @@
         <v>842</v>
       </c>
       <c r="H86" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I86" s="25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J86" s="23" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K86" s="23" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="L86" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M86" s="23" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N86" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="O86" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P86" s="25" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="Q86" s="25"/>
       <c r="R86" s="25"/>
@@ -14465,7 +14462,7 @@
       <c r="AC86" s="25"/>
       <c r="AD86" s="25"/>
       <c r="AE86" s="23" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AF86" s="25" t="str">
         <f t="shared" si="0"/>
@@ -14498,40 +14495,40 @@
         <v>-433</v>
       </c>
       <c r="H87" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="I87" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J87" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="K87" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L87" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M87" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N87" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="O87" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P87" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q87" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="I87" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J87" s="23" t="s">
+      <c r="R87" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S87" s="25" t="s">
         <v>342</v>
-      </c>
-      <c r="K87" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L87" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M87" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="N87" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="O87" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P87" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q87" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="R87" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S87" s="25" t="s">
-        <v>346</v>
       </c>
       <c r="T87" s="25">
         <v>2.75</v>
@@ -14542,7 +14539,7 @@
       </c>
       <c r="W87" s="25"/>
       <c r="X87" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y87" s="26">
         <v>4304</v>
@@ -14553,7 +14550,7 @@
       <c r="AC87" s="25"/>
       <c r="AD87" s="25"/>
       <c r="AE87" s="23" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AF87" s="25" t="str">
         <f t="shared" si="0"/>
@@ -14586,40 +14583,40 @@
         <v>215</v>
       </c>
       <c r="H88" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I88" s="25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J88" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="K88" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="L88" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M88" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="N88" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="O88" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P88" s="25" t="s">
         <v>348</v>
       </c>
-      <c r="K88" s="23" t="s">
+      <c r="Q88" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="L88" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M88" s="23" t="s">
+      <c r="R88" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S88" s="38" t="s">
         <v>350</v>
-      </c>
-      <c r="N88" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="O88" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P88" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q88" s="25" t="s">
-        <v>353</v>
-      </c>
-      <c r="R88" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S88" s="38" t="s">
-        <v>354</v>
       </c>
       <c r="T88" s="25">
         <v>5</v>
@@ -14641,7 +14638,7 @@
       <c r="AC88" s="25"/>
       <c r="AD88" s="25"/>
       <c r="AE88" s="23" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AF88" s="25" t="str">
         <f t="shared" si="0"/>
@@ -14674,40 +14671,40 @@
         <v>-447</v>
       </c>
       <c r="H89" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I89" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J89" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="K89" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L89" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M89" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N89" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="O89" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P89" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q89" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="R89" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S89" s="25" t="s">
         <v>356</v>
-      </c>
-      <c r="K89" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L89" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M89" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="N89" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="O89" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P89" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="Q89" s="25" t="s">
-        <v>359</v>
-      </c>
-      <c r="R89" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S89" s="25" t="s">
-        <v>360</v>
       </c>
       <c r="T89" s="25">
         <v>5</v>
@@ -14718,7 +14715,7 @@
       </c>
       <c r="W89" s="25"/>
       <c r="X89" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y89" s="26">
         <v>10846</v>
@@ -14729,7 +14726,7 @@
       <c r="AC89" s="25"/>
       <c r="AD89" s="25"/>
       <c r="AE89" s="23" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AF89" s="25" t="str">
         <f t="shared" si="0"/>
@@ -14762,40 +14759,40 @@
         <v>-1315</v>
       </c>
       <c r="H90" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I90" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J90" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="K90" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="L90" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M90" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N90" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O90" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P90" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q90" s="25" t="s">
         <v>362</v>
       </c>
-      <c r="K90" s="23" t="s">
+      <c r="R90" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S90" s="38" t="s">
         <v>363</v>
-      </c>
-      <c r="L90" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M90" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="N90" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O90" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P90" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q90" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="R90" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S90" s="38" t="s">
-        <v>367</v>
       </c>
       <c r="T90" s="25">
         <v>3.75</v>
@@ -14808,7 +14805,7 @@
       </c>
       <c r="W90" s="25"/>
       <c r="X90" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y90" s="26">
         <v>7064</v>
@@ -14819,7 +14816,7 @@
       <c r="AC90" s="25"/>
       <c r="AD90" s="25"/>
       <c r="AE90" s="23" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AF90" s="25" t="str">
         <f t="shared" si="0"/>
@@ -14852,36 +14849,36 @@
         <v>70</v>
       </c>
       <c r="H91" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I91" s="25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J91" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="K91" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="L91" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M91" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="N91" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="O91" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P91" s="25" t="s">
         <v>369</v>
-      </c>
-      <c r="K91" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="L91" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M91" s="23" t="s">
-        <v>371</v>
-      </c>
-      <c r="N91" s="23" t="s">
-        <v>372</v>
-      </c>
-      <c r="O91" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P91" s="25" t="s">
-        <v>373</v>
       </c>
       <c r="Q91" s="25"/>
       <c r="R91" s="25"/>
       <c r="S91" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T91" s="25">
         <v>2.5</v>
@@ -14901,7 +14898,7 @@
       <c r="AC91" s="25"/>
       <c r="AD91" s="25"/>
       <c r="AE91" s="23" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AF91" s="25" t="str">
         <f t="shared" si="0"/>
@@ -14934,36 +14931,36 @@
         <v>-49</v>
       </c>
       <c r="H92" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="I92" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J92" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="K92" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="L92" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M92" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="N92" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O92" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P92" s="25" t="s">
         <v>375</v>
-      </c>
-      <c r="I92" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J92" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="K92" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="L92" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M92" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="N92" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O92" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P92" s="25" t="s">
-        <v>379</v>
       </c>
       <c r="Q92" s="25"/>
       <c r="R92" s="25"/>
       <c r="S92" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T92" s="25">
         <v>3.7</v>
@@ -14974,7 +14971,7 @@
       </c>
       <c r="W92" s="25"/>
       <c r="X92" s="25" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="Y92" s="26">
         <v>8547</v>
@@ -14985,7 +14982,7 @@
       <c r="AC92" s="25"/>
       <c r="AD92" s="25"/>
       <c r="AE92" s="23" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="AF92" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15018,40 +15015,40 @@
         <v>-155</v>
       </c>
       <c r="H93" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I93" s="25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J93" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="K93" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L93" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M93" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="N93" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="O93" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P93" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q93" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="R93" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S93" s="25" t="s">
         <v>382</v>
-      </c>
-      <c r="K93" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L93" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M93" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="N93" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="O93" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P93" s="25" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q93" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="R93" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S93" s="25" t="s">
-        <v>386</v>
       </c>
       <c r="T93" s="25">
         <v>3</v>
@@ -15071,7 +15068,7 @@
       <c r="AC93" s="25"/>
       <c r="AD93" s="25"/>
       <c r="AE93" s="23" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AF93" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15104,31 +15101,31 @@
         <v>625</v>
       </c>
       <c r="H94" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="I94" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J94" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="K94" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="L94" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M94" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="N94" s="23" t="s">
         <v>388</v>
       </c>
-      <c r="I94" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="J94" s="23" t="s">
+      <c r="O94" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P94" s="25" t="s">
         <v>389</v>
-      </c>
-      <c r="K94" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="L94" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M94" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="N94" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="O94" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P94" s="25" t="s">
-        <v>393</v>
       </c>
       <c r="Q94" s="25"/>
       <c r="R94" s="25"/>
@@ -15153,7 +15150,7 @@
       <c r="AC94" s="25"/>
       <c r="AD94" s="25"/>
       <c r="AE94" s="23" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AF94" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15186,40 +15183,40 @@
         <v>-203</v>
       </c>
       <c r="H95" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="I95" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J95" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="K95" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="L95" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M95" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="N95" s="23" t="s">
         <v>395</v>
       </c>
-      <c r="I95" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J95" s="23" t="s">
+      <c r="O95" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P95" s="25" t="s">
         <v>396</v>
       </c>
-      <c r="K95" s="23" t="s">
+      <c r="Q95" s="25" t="s">
         <v>397</v>
       </c>
-      <c r="L95" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M95" s="23" t="s">
+      <c r="R95" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S95" s="25" t="s">
         <v>398</v>
-      </c>
-      <c r="N95" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="O95" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P95" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q95" s="25" t="s">
-        <v>401</v>
-      </c>
-      <c r="R95" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S95" s="25" t="s">
-        <v>402</v>
       </c>
       <c r="T95" s="25">
         <v>2.5</v>
@@ -15243,7 +15240,7 @@
       <c r="AC95" s="25"/>
       <c r="AD95" s="25"/>
       <c r="AE95" s="23" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AF95" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15276,31 +15273,31 @@
         <v>-49</v>
       </c>
       <c r="H96" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I96" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J96" s="23" t="s">
+        <v>400</v>
+      </c>
+      <c r="K96" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="L96" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M96" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="N96" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="O96" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P96" s="25" t="s">
         <v>404</v>
-      </c>
-      <c r="K96" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="L96" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M96" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="N96" s="23" t="s">
-        <v>407</v>
-      </c>
-      <c r="O96" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P96" s="25" t="s">
-        <v>408</v>
       </c>
       <c r="Q96" s="25"/>
       <c r="R96" s="25"/>
@@ -15325,7 +15322,7 @@
       <c r="AC96" s="25"/>
       <c r="AD96" s="25"/>
       <c r="AE96" s="23" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="AF96" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15358,40 +15355,40 @@
         <v>-111</v>
       </c>
       <c r="H97" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I97" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J97" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="K97" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="L97" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M97" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="N97" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O97" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P97" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q97" s="25" t="s">
         <v>410</v>
       </c>
-      <c r="K97" s="23" t="s">
+      <c r="R97" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S97" s="25" t="s">
         <v>411</v>
-      </c>
-      <c r="L97" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M97" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="N97" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O97" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P97" s="25" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q97" s="25" t="s">
-        <v>414</v>
-      </c>
-      <c r="R97" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S97" s="25" t="s">
-        <v>415</v>
       </c>
       <c r="T97" s="25">
         <v>3.5</v>
@@ -15404,7 +15401,7 @@
         <v>2</v>
       </c>
       <c r="X97" s="25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="Y97" s="26">
         <v>7239</v>
@@ -15446,40 +15443,40 @@
         <v>-473</v>
       </c>
       <c r="H98" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="I98" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J98" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="K98" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="L98" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M98" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="N98" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O98" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P98" s="25" t="s">
         <v>416</v>
       </c>
-      <c r="I98" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J98" s="23" t="s">
+      <c r="Q98" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="K98" s="23" t="s">
+      <c r="R98" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S98" s="38" t="s">
         <v>418</v>
-      </c>
-      <c r="L98" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M98" s="23" t="s">
-        <v>419</v>
-      </c>
-      <c r="N98" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O98" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P98" s="25" t="s">
-        <v>420</v>
-      </c>
-      <c r="Q98" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="R98" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S98" s="38" t="s">
-        <v>422</v>
       </c>
       <c r="T98" s="25">
         <v>1.2</v>
@@ -15534,31 +15531,31 @@
         <v>740</v>
       </c>
       <c r="H99" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="I99" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J99" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="K99" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="L99" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M99" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="N99" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="I99" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="J99" s="23" t="s">
+      <c r="O99" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P99" s="25" t="s">
         <v>424</v>
-      </c>
-      <c r="K99" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="L99" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M99" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="N99" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="O99" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P99" s="25" t="s">
-        <v>428</v>
       </c>
       <c r="Q99" s="25"/>
       <c r="R99" s="25"/>
@@ -15574,7 +15571,7 @@
       </c>
       <c r="W99" s="25"/>
       <c r="X99" s="25" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="Y99" s="26">
         <v>14032</v>
@@ -15587,7 +15584,7 @@
       <c r="AC99" s="25"/>
       <c r="AD99" s="25"/>
       <c r="AE99" s="23" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AF99" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15620,40 +15617,40 @@
         <v>-250</v>
       </c>
       <c r="H100" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I100" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J100" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="K100" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="L100" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M100" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="N100" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O100" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P100" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q100" s="25" t="s">
         <v>431</v>
       </c>
-      <c r="K100" s="23" t="s">
+      <c r="R100" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S100" s="38" t="s">
         <v>432</v>
-      </c>
-      <c r="L100" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M100" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="N100" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O100" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P100" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q100" s="25" t="s">
-        <v>435</v>
-      </c>
-      <c r="R100" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S100" s="38" t="s">
-        <v>436</v>
       </c>
       <c r="T100" s="25">
         <v>2.1</v>
@@ -15673,7 +15670,7 @@
       <c r="AC100" s="25"/>
       <c r="AD100" s="25"/>
       <c r="AE100" s="23" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AF100" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15706,40 +15703,40 @@
         <v>-606</v>
       </c>
       <c r="H101" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="I101" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J101" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="K101" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="L101" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M101" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="N101" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="O101" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P101" s="25" t="s">
         <v>438</v>
       </c>
-      <c r="I101" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J101" s="23" t="s">
+      <c r="Q101" s="25" t="s">
         <v>439</v>
       </c>
-      <c r="K101" s="23" t="s">
+      <c r="R101" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S101" s="25" t="s">
         <v>440</v>
-      </c>
-      <c r="L101" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M101" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="N101" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O101" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P101" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q101" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="R101" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S101" s="25" t="s">
-        <v>444</v>
       </c>
       <c r="T101" s="25">
         <v>2.5</v>
@@ -15763,7 +15760,7 @@
       <c r="AC101" s="25"/>
       <c r="AD101" s="25"/>
       <c r="AE101" s="23" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AF101" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15796,40 +15793,40 @@
         <v>-377</v>
       </c>
       <c r="H102" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="I102" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J102" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="K102" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="L102" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M102" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="N102" s="23" t="s">
         <v>446</v>
       </c>
-      <c r="I102" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J102" s="23" t="s">
+      <c r="O102" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P102" s="25" t="s">
         <v>447</v>
       </c>
-      <c r="K102" s="23" t="s">
+      <c r="Q102" s="25" t="s">
         <v>448</v>
       </c>
-      <c r="L102" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M102" s="23" t="s">
+      <c r="R102" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S102" s="25" t="s">
         <v>449</v>
-      </c>
-      <c r="N102" s="23" t="s">
-        <v>450</v>
-      </c>
-      <c r="O102" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P102" s="25" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q102" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="R102" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S102" s="25" t="s">
-        <v>453</v>
       </c>
       <c r="T102" s="25">
         <v>3</v>
@@ -15850,10 +15847,10 @@
       <c r="AB102" s="25"/>
       <c r="AC102" s="25"/>
       <c r="AD102" s="25" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AE102" s="23" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AF102" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15886,40 +15883,40 @@
         <v>-63</v>
       </c>
       <c r="H103" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="I103" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J103" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="K103" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="L103" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M103" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="N103" s="23" t="s">
         <v>456</v>
       </c>
-      <c r="I103" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J103" s="23" t="s">
+      <c r="O103" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P103" s="25" t="s">
         <v>457</v>
       </c>
-      <c r="K103" s="23" t="s">
+      <c r="Q103" s="25" t="s">
         <v>458</v>
       </c>
-      <c r="L103" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M103" s="23" t="s">
+      <c r="R103" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S103" s="25" t="s">
         <v>459</v>
-      </c>
-      <c r="N103" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="O103" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P103" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q103" s="25" t="s">
-        <v>462</v>
-      </c>
-      <c r="R103" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S103" s="25" t="s">
-        <v>463</v>
       </c>
       <c r="T103" s="25">
         <v>3.9</v>
@@ -15942,10 +15939,10 @@
       <c r="AB103" s="40"/>
       <c r="AC103" s="25"/>
       <c r="AD103" s="25" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AE103" s="23" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AF103" s="25" t="str">
         <f t="shared" si="0"/>
@@ -15978,40 +15975,40 @@
         <v>-20</v>
       </c>
       <c r="H104" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="I104" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J104" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="K104" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L104" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M104" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="N104" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="O104" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P104" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="I104" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="J104" s="23" t="s">
+      <c r="Q104" s="25" t="s">
         <v>466</v>
       </c>
-      <c r="K104" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L104" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M104" s="23" t="s">
+      <c r="R104" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S104" s="25" t="s">
         <v>467</v>
-      </c>
-      <c r="N104" s="23" t="s">
-        <v>468</v>
-      </c>
-      <c r="O104" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P104" s="25" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q104" s="25" t="s">
-        <v>470</v>
-      </c>
-      <c r="R104" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S104" s="25" t="s">
-        <v>471</v>
       </c>
       <c r="T104" s="25">
         <v>4</v>
@@ -16034,10 +16031,10 @@
       <c r="AB104" s="25"/>
       <c r="AC104" s="25"/>
       <c r="AD104" s="25" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="AE104" s="23" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="AF104" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16070,31 +16067,31 @@
         <v>293</v>
       </c>
       <c r="H105" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="I105" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J105" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="K105" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="L105" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M105" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="N105" s="23" t="s">
         <v>474</v>
       </c>
-      <c r="I105" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J105" s="23" t="s">
+      <c r="O105" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P105" s="25" t="s">
         <v>475</v>
-      </c>
-      <c r="K105" s="23" t="s">
-        <v>476</v>
-      </c>
-      <c r="L105" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M105" s="23" t="s">
-        <v>477</v>
-      </c>
-      <c r="N105" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="O105" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P105" s="25" t="s">
-        <v>479</v>
       </c>
       <c r="Q105" s="25"/>
       <c r="R105" s="25"/>
@@ -16120,10 +16117,10 @@
       <c r="AB105" s="25"/>
       <c r="AC105" s="25"/>
       <c r="AD105" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE105" s="23" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AF105" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16156,31 +16153,31 @@
         <v>-75</v>
       </c>
       <c r="H106" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="I106" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J106" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="K106" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="L106" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M106" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="N106" s="23" t="s">
         <v>481</v>
       </c>
-      <c r="I106" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="J106" s="23" t="s">
+      <c r="O106" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P106" s="25" t="s">
         <v>482</v>
-      </c>
-      <c r="K106" s="23" t="s">
-        <v>483</v>
-      </c>
-      <c r="L106" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M106" s="23" t="s">
-        <v>484</v>
-      </c>
-      <c r="N106" s="23" t="s">
-        <v>485</v>
-      </c>
-      <c r="O106" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P106" s="25" t="s">
-        <v>486</v>
       </c>
       <c r="Q106" s="25"/>
       <c r="R106" s="25"/>
@@ -16204,10 +16201,10 @@
       <c r="AB106" s="25"/>
       <c r="AC106" s="25"/>
       <c r="AD106" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE106" s="23" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="AF106" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16240,40 +16237,40 @@
         <v>-100</v>
       </c>
       <c r="H107" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="I107" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J107" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="K107" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="L107" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M107" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="N107" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="O107" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P107" s="25" t="s">
         <v>488</v>
       </c>
-      <c r="I107" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J107" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="K107" s="23" t="s">
+      <c r="Q107" s="25" t="s">
         <v>489</v>
       </c>
-      <c r="L107" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M107" s="23" t="s">
+      <c r="R107" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S107" s="25" t="s">
         <v>490</v>
-      </c>
-      <c r="N107" s="23" t="s">
-        <v>491</v>
-      </c>
-      <c r="O107" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P107" s="25" t="s">
-        <v>492</v>
-      </c>
-      <c r="Q107" s="25" t="s">
-        <v>493</v>
-      </c>
-      <c r="R107" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S107" s="25" t="s">
-        <v>494</v>
       </c>
       <c r="T107" s="25">
         <v>4</v>
@@ -16284,7 +16281,7 @@
       </c>
       <c r="W107" s="25"/>
       <c r="X107" s="25" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="Y107" s="26">
         <v>7000</v>
@@ -16295,13 +16292,13 @@
       </c>
       <c r="AB107" s="25"/>
       <c r="AC107" s="25" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="AD107" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE107" s="23" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AF107" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16334,31 +16331,31 @@
         <v>300</v>
       </c>
       <c r="H108" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="I108" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J108" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="K108" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="L108" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M108" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="N108" s="23" t="s">
         <v>498</v>
       </c>
-      <c r="I108" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="J108" s="23" t="s">
+      <c r="O108" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P108" s="25" t="s">
         <v>499</v>
-      </c>
-      <c r="K108" s="23" t="s">
-        <v>500</v>
-      </c>
-      <c r="L108" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M108" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="N108" s="23" t="s">
-        <v>502</v>
-      </c>
-      <c r="O108" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P108" s="25" t="s">
-        <v>503</v>
       </c>
       <c r="Q108" s="25"/>
       <c r="R108" s="25"/>
@@ -16381,11 +16378,11 @@
       <c r="AA108" s="28"/>
       <c r="AB108" s="25"/>
       <c r="AC108" s="25" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AD108" s="25"/>
       <c r="AE108" s="23" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AF108" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16418,40 +16415,40 @@
         <v>327</v>
       </c>
       <c r="H109" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="I109" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J109" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="K109" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="L109" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M109" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="N109" s="23" t="s">
         <v>506</v>
       </c>
-      <c r="I109" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J109" s="23" t="s">
+      <c r="O109" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P109" s="25" t="s">
         <v>507</v>
       </c>
-      <c r="K109" s="23" t="s">
+      <c r="Q109" s="25" t="s">
         <v>508</v>
       </c>
-      <c r="L109" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M109" s="23" t="s">
+      <c r="R109" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S109" s="25" t="s">
         <v>509</v>
-      </c>
-      <c r="N109" s="23" t="s">
-        <v>510</v>
-      </c>
-      <c r="O109" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P109" s="25" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q109" s="25" t="s">
-        <v>512</v>
-      </c>
-      <c r="R109" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S109" s="25" t="s">
-        <v>513</v>
       </c>
       <c r="T109" s="25">
         <v>4</v>
@@ -16473,13 +16470,13 @@
       <c r="AA109" s="28"/>
       <c r="AB109" s="25"/>
       <c r="AC109" s="25" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="AD109" s="25" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AE109" s="23" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AF109" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16512,34 +16509,34 @@
         <v>-38</v>
       </c>
       <c r="H110" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I110" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J110" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="K110" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="L110" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M110" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="N110" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="O110" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P110" s="25" t="s">
         <v>516</v>
       </c>
-      <c r="K110" s="23" t="s">
-        <v>517</v>
-      </c>
-      <c r="L110" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M110" s="23" t="s">
-        <v>518</v>
-      </c>
-      <c r="N110" s="23" t="s">
-        <v>519</v>
-      </c>
-      <c r="O110" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P110" s="25" t="s">
-        <v>520</v>
-      </c>
       <c r="Q110" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="R110" s="25"/>
       <c r="S110" s="25"/>
@@ -16563,13 +16560,13 @@
       <c r="AA110" s="28"/>
       <c r="AB110" s="25"/>
       <c r="AC110" s="25" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="AD110" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE110" s="23" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AF110" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16603,37 +16600,37 @@
       </c>
       <c r="H111" s="23"/>
       <c r="I111" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J111" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="K111" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="L111" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M111" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="N111" s="42" t="s">
+        <v>522</v>
+      </c>
+      <c r="O111" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P111" s="43" t="s">
         <v>523</v>
       </c>
-      <c r="K111" s="23" t="s">
+      <c r="Q111" s="43" t="s">
         <v>524</v>
       </c>
-      <c r="L111" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M111" s="23" t="s">
+      <c r="R111" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S111" s="43" t="s">
         <v>525</v>
-      </c>
-      <c r="N111" s="42" t="s">
-        <v>526</v>
-      </c>
-      <c r="O111" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P111" s="43" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q111" s="43" t="s">
-        <v>528</v>
-      </c>
-      <c r="R111" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S111" s="43" t="s">
-        <v>529</v>
       </c>
       <c r="T111" s="25">
         <v>4</v>
@@ -16655,11 +16652,11 @@
       </c>
       <c r="AB111" s="25"/>
       <c r="AC111" s="25" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AD111" s="25"/>
       <c r="AE111" s="23" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="AF111" s="25" t="str">
         <f t="shared" si="0"/>
@@ -16695,37 +16692,37 @@
         <v>0</v>
       </c>
       <c r="I112" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J112" s="23" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="K112" s="23">
         <v>0</v>
       </c>
       <c r="L112" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M112" s="23" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="N112" s="23">
         <v>0</v>
       </c>
       <c r="O112" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P112" s="25" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="Q112" s="25" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="R112" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S112" s="25" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="T112" s="25">
         <v>1.9</v>
@@ -16747,7 +16744,7 @@
       <c r="AC112" s="25"/>
       <c r="AD112" s="25"/>
       <c r="AE112" s="23" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AF112" s="25" t="str">
         <f t="shared" ref="AF112:AF155" si="1">IF( ((I112="Rot")*2 + (L112="Rot")*2 + (O112="Rot")*2 + (R112="Rot")*2 + (I112="Gelb") + (L112="Gelb") + (O112="Gelb") + (R112="Gelb")) &gt;= 4, "Rot", IF( ((I112="Rot")*2 + (L112="Rot")*2 + (O112="Rot")*2 + (R112="Rot")*2 + (I112="Gelb") + (L112="Gelb") + (O112="Gelb") + (R112="Gelb")) &gt;= 2, "Gelb", "Grün" ) )</f>
@@ -16780,40 +16777,40 @@
         <v>450</v>
       </c>
       <c r="H113" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="I113" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J113" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="K113" s="23" t="s">
+        <v>536</v>
+      </c>
+      <c r="L113" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M113" s="23" t="s">
+        <v>537</v>
+      </c>
+      <c r="N113" s="23" t="s">
         <v>538</v>
       </c>
-      <c r="I113" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J113" s="23" t="s">
+      <c r="O113" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P113" s="25" t="s">
         <v>539</v>
       </c>
-      <c r="K113" s="23" t="s">
+      <c r="Q113" s="25" t="s">
         <v>540</v>
       </c>
-      <c r="L113" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M113" s="23" t="s">
+      <c r="R113" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S113" s="25" t="s">
         <v>541</v>
-      </c>
-      <c r="N113" s="23" t="s">
-        <v>542</v>
-      </c>
-      <c r="O113" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P113" s="25" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q113" s="25" t="s">
-        <v>544</v>
-      </c>
-      <c r="R113" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S113" s="25" t="s">
-        <v>545</v>
       </c>
       <c r="T113" s="25">
         <v>4.2</v>
@@ -16837,7 +16834,7 @@
       <c r="AC113" s="25"/>
       <c r="AD113" s="25"/>
       <c r="AE113" s="23" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AF113" s="25" t="str">
         <f t="shared" si="1"/>
@@ -16870,40 +16867,40 @@
         <v>20</v>
       </c>
       <c r="H114" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I114" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J114" s="23" t="s">
+        <v>543</v>
+      </c>
+      <c r="K114" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="L114" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M114" s="23" t="s">
+        <v>545</v>
+      </c>
+      <c r="N114" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="O114" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P114" s="25" t="s">
         <v>547</v>
       </c>
-      <c r="K114" s="23" t="s">
+      <c r="Q114" s="25" t="s">
         <v>548</v>
       </c>
-      <c r="L114" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M114" s="23" t="s">
+      <c r="R114" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S114" s="25" t="s">
         <v>549</v>
-      </c>
-      <c r="N114" s="23" t="s">
-        <v>550</v>
-      </c>
-      <c r="O114" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P114" s="25" t="s">
-        <v>551</v>
-      </c>
-      <c r="Q114" s="25" t="s">
-        <v>552</v>
-      </c>
-      <c r="R114" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S114" s="25" t="s">
-        <v>553</v>
       </c>
       <c r="T114" s="25">
         <v>1.8</v>
@@ -16916,7 +16913,7 @@
         <v>3</v>
       </c>
       <c r="X114" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y114" s="26">
         <v>7114</v>
@@ -16926,12 +16923,12 @@
         <v>12.95</v>
       </c>
       <c r="AB114" s="25" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AC114" s="25"/>
       <c r="AD114" s="25"/>
       <c r="AE114" s="23" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AF114" s="25" t="str">
         <f t="shared" si="1"/>
@@ -16964,38 +16961,38 @@
         <v>555</v>
       </c>
       <c r="H115" s="23" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="I115" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J115" s="23"/>
       <c r="K115" s="23" t="s">
+        <v>553</v>
+      </c>
+      <c r="L115" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M115" s="23" t="s">
+        <v>554</v>
+      </c>
+      <c r="N115" s="23" t="s">
+        <v>555</v>
+      </c>
+      <c r="O115" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P115" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q115" s="25" t="s">
         <v>557</v>
       </c>
-      <c r="L115" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M115" s="23" t="s">
+      <c r="R115" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S115" s="25" t="s">
         <v>558</v>
-      </c>
-      <c r="N115" s="23" t="s">
-        <v>559</v>
-      </c>
-      <c r="O115" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P115" s="25" t="s">
-        <v>560</v>
-      </c>
-      <c r="Q115" s="25" t="s">
-        <v>561</v>
-      </c>
-      <c r="R115" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S115" s="25" t="s">
-        <v>562</v>
       </c>
       <c r="T115" s="25">
         <v>4</v>
@@ -17008,7 +17005,7 @@
       </c>
       <c r="W115" s="25"/>
       <c r="X115" s="25" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="Y115" s="26">
         <v>8676</v>
@@ -17018,10 +17015,10 @@
       <c r="AB115" s="25"/>
       <c r="AC115" s="25"/>
       <c r="AD115" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE115" s="23" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="AF115" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17054,40 +17051,40 @@
         <v>70</v>
       </c>
       <c r="H116" s="23" t="s">
+        <v>561</v>
+      </c>
+      <c r="I116" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J116" s="23" t="s">
+        <v>562</v>
+      </c>
+      <c r="K116" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="L116" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M116" s="23" t="s">
+        <v>564</v>
+      </c>
+      <c r="N116" s="23" t="s">
         <v>565</v>
       </c>
-      <c r="I116" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J116" s="23" t="s">
+      <c r="O116" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P116" s="25" t="s">
         <v>566</v>
       </c>
-      <c r="K116" s="23" t="s">
+      <c r="Q116" s="25" t="s">
         <v>567</v>
       </c>
-      <c r="L116" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M116" s="23" t="s">
+      <c r="R116" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S116" s="25" t="s">
         <v>568</v>
-      </c>
-      <c r="N116" s="23" t="s">
-        <v>569</v>
-      </c>
-      <c r="O116" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P116" s="25" t="s">
-        <v>570</v>
-      </c>
-      <c r="Q116" s="25" t="s">
-        <v>571</v>
-      </c>
-      <c r="R116" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S116" s="25" t="s">
-        <v>572</v>
       </c>
       <c r="T116" s="25">
         <v>4.7</v>
@@ -17108,10 +17105,10 @@
       <c r="AB116" s="25"/>
       <c r="AC116" s="25"/>
       <c r="AD116" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE116" s="23" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AF116" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17137,50 +17134,50 @@
         <v>1785</v>
       </c>
       <c r="F117" s="27" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G117" s="21">
         <f>Masterfile!$E117-2200</f>
         <v>-415</v>
       </c>
       <c r="H117" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I117" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J117" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K117" s="23" t="s">
+        <v>571</v>
+      </c>
+      <c r="L117" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M117" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="N117" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="O117" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P117" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="Q117" s="25" t="s">
         <v>575</v>
       </c>
-      <c r="L117" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M117" s="23" t="s">
+      <c r="R117" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S117" s="25" t="s">
         <v>576</v>
       </c>
-      <c r="N117" s="23" t="s">
+      <c r="T117" s="25" t="s">
         <v>577</v>
-      </c>
-      <c r="O117" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P117" s="25" t="s">
-        <v>578</v>
-      </c>
-      <c r="Q117" s="25" t="s">
-        <v>579</v>
-      </c>
-      <c r="R117" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S117" s="25" t="s">
-        <v>580</v>
-      </c>
-      <c r="T117" s="25" t="s">
-        <v>581</v>
       </c>
       <c r="U117" s="25">
         <v>1</v>
@@ -17198,16 +17195,16 @@
         <v>17.079999999999998</v>
       </c>
       <c r="AB117" s="25" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AC117" s="25" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AD117" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE117" s="23" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AF117" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17233,47 +17230,47 @@
         <v>1650</v>
       </c>
       <c r="F118" s="27" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G118" s="21">
         <f>Masterfile!$E118-2200</f>
         <v>-550</v>
       </c>
       <c r="H118" s="23" t="s">
+        <v>582</v>
+      </c>
+      <c r="I118" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J118" s="23" t="s">
+        <v>583</v>
+      </c>
+      <c r="K118" s="23" t="s">
+        <v>584</v>
+      </c>
+      <c r="L118" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M118" s="23" t="s">
+        <v>585</v>
+      </c>
+      <c r="N118" s="23" t="s">
         <v>586</v>
       </c>
-      <c r="I118" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="J118" s="23" t="s">
+      <c r="O118" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P118" s="25" t="s">
         <v>587</v>
       </c>
-      <c r="K118" s="23" t="s">
+      <c r="Q118" s="25" t="s">
         <v>588</v>
       </c>
-      <c r="L118" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M118" s="23" t="s">
+      <c r="R118" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S118" s="25" t="s">
         <v>589</v>
-      </c>
-      <c r="N118" s="23" t="s">
-        <v>590</v>
-      </c>
-      <c r="O118" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P118" s="25" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q118" s="25" t="s">
-        <v>592</v>
-      </c>
-      <c r="R118" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="S118" s="25" t="s">
-        <v>593</v>
       </c>
       <c r="T118" s="25">
         <v>3</v>
@@ -17288,7 +17285,7 @@
         <v>3</v>
       </c>
       <c r="X118" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y118" s="26">
         <v>8990</v>
@@ -17299,13 +17296,13 @@
       </c>
       <c r="AB118" s="25"/>
       <c r="AC118" s="25" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="AD118" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE118" s="23" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="AF118" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17338,40 +17335,40 @@
         <v>-150</v>
       </c>
       <c r="H119" s="23" t="s">
+        <v>592</v>
+      </c>
+      <c r="I119" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J119" s="23" t="s">
+        <v>593</v>
+      </c>
+      <c r="K119" s="23" t="s">
+        <v>594</v>
+      </c>
+      <c r="L119" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M119" s="23" t="s">
+        <v>595</v>
+      </c>
+      <c r="N119" s="23" t="s">
         <v>596</v>
       </c>
-      <c r="I119" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J119" s="23" t="s">
+      <c r="O119" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P119" s="25" t="s">
         <v>597</v>
       </c>
-      <c r="K119" s="23" t="s">
+      <c r="Q119" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="L119" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M119" s="23" t="s">
+      <c r="R119" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S119" s="25" t="s">
         <v>599</v>
-      </c>
-      <c r="N119" s="23" t="s">
-        <v>600</v>
-      </c>
-      <c r="O119" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P119" s="25" t="s">
-        <v>601</v>
-      </c>
-      <c r="Q119" s="25" t="s">
-        <v>602</v>
-      </c>
-      <c r="R119" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S119" s="25" t="s">
-        <v>603</v>
       </c>
       <c r="T119" s="25">
         <v>3.5</v>
@@ -17384,7 +17381,7 @@
       </c>
       <c r="W119" s="25"/>
       <c r="X119" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y119" s="26">
         <v>9060</v>
@@ -17394,14 +17391,14 @@
         <v>38.159999999999997</v>
       </c>
       <c r="AB119" s="25" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AC119" s="25" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="AD119" s="25"/>
       <c r="AE119" s="23" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="AF119" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17434,40 +17431,40 @@
         <v>-250</v>
       </c>
       <c r="H120" s="23" t="s">
+        <v>603</v>
+      </c>
+      <c r="I120" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J120" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="K120" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L120" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M120" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="N120" s="23" t="s">
+        <v>605</v>
+      </c>
+      <c r="O120" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P120" s="25" t="s">
+        <v>606</v>
+      </c>
+      <c r="Q120" s="25" t="s">
         <v>607</v>
       </c>
-      <c r="I120" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J120" s="23" t="s">
+      <c r="R120" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S120" s="25" t="s">
         <v>608</v>
-      </c>
-      <c r="K120" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L120" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M120" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="N120" s="23" t="s">
-        <v>609</v>
-      </c>
-      <c r="O120" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P120" s="25" t="s">
-        <v>610</v>
-      </c>
-      <c r="Q120" s="25" t="s">
-        <v>611</v>
-      </c>
-      <c r="R120" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S120" s="25" t="s">
-        <v>612</v>
       </c>
       <c r="T120" s="25">
         <v>3.2</v>
@@ -17478,7 +17475,7 @@
       </c>
       <c r="W120" s="25"/>
       <c r="X120" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y120" s="26">
         <v>6097</v>
@@ -17488,12 +17485,12 @@
         <v>12.66</v>
       </c>
       <c r="AB120" s="25" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="AC120" s="25"/>
       <c r="AD120" s="25"/>
       <c r="AE120" s="23" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="AF120" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17526,40 +17523,40 @@
         <v>-560</v>
       </c>
       <c r="H121" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I121" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J121" s="23" t="s">
+        <v>611</v>
+      </c>
+      <c r="K121" s="23" t="s">
+        <v>612</v>
+      </c>
+      <c r="L121" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M121" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="N121" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="O121" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P121" s="25" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q121" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="K121" s="23" t="s">
+      <c r="R121" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S121" s="25" t="s">
         <v>616</v>
-      </c>
-      <c r="L121" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M121" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="N121" s="23" t="s">
-        <v>617</v>
-      </c>
-      <c r="O121" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P121" s="25" t="s">
-        <v>618</v>
-      </c>
-      <c r="Q121" s="25" t="s">
-        <v>619</v>
-      </c>
-      <c r="R121" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S121" s="25" t="s">
-        <v>620</v>
       </c>
       <c r="T121" s="25">
         <v>3.3</v>
@@ -17570,7 +17567,7 @@
       </c>
       <c r="W121" s="25"/>
       <c r="X121" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y121" s="26">
         <v>2567</v>
@@ -17581,13 +17578,13 @@
       </c>
       <c r="AB121" s="25"/>
       <c r="AC121" s="25" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="AD121" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AE121" s="23" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="AF121" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17618,40 +17615,40 @@
         <v>-2200</v>
       </c>
       <c r="H122" s="26" t="s">
+        <v>619</v>
+      </c>
+      <c r="I122" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J122" s="25" t="s">
+        <v>620</v>
+      </c>
+      <c r="K122" s="23" t="s">
+        <v>621</v>
+      </c>
+      <c r="L122" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M122" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="N122" s="23" t="s">
         <v>623</v>
       </c>
-      <c r="I122" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J122" s="25" t="s">
+      <c r="O122" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P122" s="25" t="s">
         <v>624</v>
       </c>
-      <c r="K122" s="23" t="s">
+      <c r="Q122" s="25" t="s">
         <v>625</v>
       </c>
-      <c r="L122" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M122" s="25" t="s">
+      <c r="R122" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S122" s="25" t="s">
         <v>626</v>
-      </c>
-      <c r="N122" s="23" t="s">
-        <v>627</v>
-      </c>
-      <c r="O122" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P122" s="25" t="s">
-        <v>628</v>
-      </c>
-      <c r="Q122" s="25" t="s">
-        <v>629</v>
-      </c>
-      <c r="R122" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S122" s="25" t="s">
-        <v>630</v>
       </c>
       <c r="T122" s="25">
         <v>4.4000000000000004</v>
@@ -17672,14 +17669,14 @@
         <v>12</v>
       </c>
       <c r="AB122" s="25" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="AC122" s="25" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="AD122" s="25"/>
       <c r="AE122" s="25" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="AF122" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17712,40 +17709,40 @@
         <v>-360</v>
       </c>
       <c r="H123" s="26" t="s">
+        <v>630</v>
+      </c>
+      <c r="I123" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J123" s="25" t="s">
+        <v>631</v>
+      </c>
+      <c r="K123" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="L123" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M123" s="25" t="s">
+        <v>633</v>
+      </c>
+      <c r="N123" s="23" t="s">
         <v>634</v>
       </c>
-      <c r="I123" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J123" s="25" t="s">
+      <c r="O123" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P123" s="25" t="s">
         <v>635</v>
       </c>
-      <c r="K123" s="23" t="s">
+      <c r="Q123" s="25" t="s">
         <v>636</v>
       </c>
-      <c r="L123" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M123" s="25" t="s">
+      <c r="R123" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S123" s="25" t="s">
         <v>637</v>
-      </c>
-      <c r="N123" s="23" t="s">
-        <v>638</v>
-      </c>
-      <c r="O123" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P123" s="25" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q123" s="25" t="s">
-        <v>640</v>
-      </c>
-      <c r="R123" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S123" s="25" t="s">
-        <v>641</v>
       </c>
       <c r="T123" s="25">
         <v>3.2</v>
@@ -17767,13 +17764,13 @@
       <c r="AA123" s="28"/>
       <c r="AB123" s="25"/>
       <c r="AC123" s="25" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="AD123" s="25" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="AE123" s="25" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="AF123" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17806,40 +17803,40 @@
         <v>-105</v>
       </c>
       <c r="H124" s="25" t="s">
+        <v>641</v>
+      </c>
+      <c r="I124" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J124" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="K124" s="23" t="s">
+        <v>643</v>
+      </c>
+      <c r="L124" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M124" s="25" t="s">
+        <v>644</v>
+      </c>
+      <c r="N124" s="23" t="s">
         <v>645</v>
       </c>
-      <c r="I124" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J124" s="25" t="s">
+      <c r="O124" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P124" s="25" t="s">
         <v>646</v>
       </c>
-      <c r="K124" s="23" t="s">
+      <c r="Q124" s="25" t="s">
         <v>647</v>
       </c>
-      <c r="L124" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M124" s="25" t="s">
+      <c r="R124" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S124" s="25" t="s">
         <v>648</v>
-      </c>
-      <c r="N124" s="23" t="s">
-        <v>649</v>
-      </c>
-      <c r="O124" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P124" s="25" t="s">
-        <v>650</v>
-      </c>
-      <c r="Q124" s="25" t="s">
-        <v>651</v>
-      </c>
-      <c r="R124" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S124" s="25" t="s">
-        <v>652</v>
       </c>
       <c r="T124" s="25">
         <v>3.2</v>
@@ -17863,13 +17860,13 @@
       <c r="AA124" s="28"/>
       <c r="AB124" s="25"/>
       <c r="AC124" s="25" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="AD124" s="25" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="AE124" s="25" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="AF124" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17902,40 +17899,40 @@
         <v>50</v>
       </c>
       <c r="H125" s="23" t="s">
+        <v>652</v>
+      </c>
+      <c r="I125" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J125" s="23" t="s">
+        <v>606</v>
+      </c>
+      <c r="K125" s="23" t="s">
+        <v>653</v>
+      </c>
+      <c r="L125" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M125" s="23" t="s">
+        <v>654</v>
+      </c>
+      <c r="N125" s="23" t="s">
+        <v>655</v>
+      </c>
+      <c r="O125" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P125" s="25" t="s">
         <v>656</v>
       </c>
-      <c r="I125" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J125" s="23" t="s">
-        <v>610</v>
-      </c>
-      <c r="K125" s="23" t="s">
+      <c r="Q125" s="25" t="s">
         <v>657</v>
       </c>
-      <c r="L125" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M125" s="23" t="s">
+      <c r="R125" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S125" s="25" t="s">
         <v>658</v>
-      </c>
-      <c r="N125" s="23" t="s">
-        <v>659</v>
-      </c>
-      <c r="O125" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P125" s="25" t="s">
-        <v>660</v>
-      </c>
-      <c r="Q125" s="25" t="s">
-        <v>661</v>
-      </c>
-      <c r="R125" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="S125" s="25" t="s">
-        <v>662</v>
       </c>
       <c r="T125" s="25">
         <v>3</v>
@@ -17950,7 +17947,7 @@
         <v>1</v>
       </c>
       <c r="X125" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Y125" s="26">
         <v>7375</v>
@@ -17961,11 +17958,11 @@
       </c>
       <c r="AB125" s="25"/>
       <c r="AC125" s="25" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="AD125" s="25"/>
       <c r="AE125" s="23" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="AF125" s="25" t="str">
         <f t="shared" si="1"/>
@@ -17998,43 +17995,43 @@
         <v>-575</v>
       </c>
       <c r="H126" s="23" t="s">
+        <v>661</v>
+      </c>
+      <c r="I126" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J126" s="23" t="s">
+        <v>662</v>
+      </c>
+      <c r="K126" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="L126" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M126" s="23" t="s">
+        <v>663</v>
+      </c>
+      <c r="N126" s="23" t="s">
+        <v>664</v>
+      </c>
+      <c r="O126" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P126" s="25" t="s">
         <v>665</v>
       </c>
-      <c r="I126" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J126" s="23" t="s">
+      <c r="Q126" s="25" t="s">
         <v>666</v>
       </c>
-      <c r="K126" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L126" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M126" s="23" t="s">
+      <c r="R126" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S126" s="25" t="s">
         <v>667</v>
       </c>
-      <c r="N126" s="23" t="s">
+      <c r="T126" s="25" t="s">
         <v>668</v>
-      </c>
-      <c r="O126" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P126" s="25" t="s">
-        <v>669</v>
-      </c>
-      <c r="Q126" s="25" t="s">
-        <v>670</v>
-      </c>
-      <c r="R126" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S126" s="25" t="s">
-        <v>671</v>
-      </c>
-      <c r="T126" s="25" t="s">
-        <v>672</v>
       </c>
       <c r="U126" s="25">
         <v>1</v>
@@ -18046,7 +18043,7 @@
         <v>2</v>
       </c>
       <c r="X126" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Y126" s="26">
         <v>7083</v>
@@ -18056,14 +18053,14 @@
         <v>12</v>
       </c>
       <c r="AB126" s="25" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="AC126" s="25" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="AD126" s="25"/>
       <c r="AE126" s="23" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="AF126" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18096,40 +18093,40 @@
         <v>-514</v>
       </c>
       <c r="H127" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I127" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J127" s="23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K127" s="23" t="s">
+        <v>672</v>
+      </c>
+      <c r="L127" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M127" s="23" t="s">
+        <v>673</v>
+      </c>
+      <c r="N127" s="23" t="s">
+        <v>674</v>
+      </c>
+      <c r="O127" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P127" s="25" t="s">
+        <v>675</v>
+      </c>
+      <c r="Q127" s="25" t="s">
         <v>676</v>
       </c>
-      <c r="L127" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M127" s="23" t="s">
+      <c r="R127" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S127" s="25" t="s">
         <v>677</v>
-      </c>
-      <c r="N127" s="23" t="s">
-        <v>678</v>
-      </c>
-      <c r="O127" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P127" s="25" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q127" s="25" t="s">
-        <v>680</v>
-      </c>
-      <c r="R127" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="S127" s="25" t="s">
-        <v>681</v>
       </c>
       <c r="T127" s="25">
         <v>3.3</v>
@@ -18142,7 +18139,7 @@
       </c>
       <c r="W127" s="25"/>
       <c r="X127" s="25" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="Y127" s="26">
         <v>11000</v>
@@ -18152,14 +18149,14 @@
         <v>33.21</v>
       </c>
       <c r="AB127" s="25" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="AC127" s="25" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="AD127" s="25"/>
       <c r="AE127" s="23" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="AF127" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18192,38 +18189,38 @@
         <v>230</v>
       </c>
       <c r="H128" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="I128" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J128" s="23" t="s">
+        <v>683</v>
+      </c>
+      <c r="K128" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="L128" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M128" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="N128" s="23" t="s">
         <v>686</v>
       </c>
-      <c r="I128" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J128" s="23" t="s">
+      <c r="O128" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P128" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="K128" s="23" t="s">
-        <v>688</v>
-      </c>
-      <c r="L128" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M128" s="23" t="s">
-        <v>689</v>
-      </c>
-      <c r="N128" s="23" t="s">
-        <v>690</v>
-      </c>
-      <c r="O128" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P128" s="25" t="s">
-        <v>691</v>
-      </c>
       <c r="Q128" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="R128" s="25"/>
       <c r="S128" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T128" s="25">
         <v>3.7</v>
@@ -18246,14 +18243,14 @@
         <v>12</v>
       </c>
       <c r="AB128" s="25" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="AC128" s="25" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="AD128" s="25"/>
       <c r="AE128" s="23" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="AF128" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18286,40 +18283,40 @@
         <v>-162</v>
       </c>
       <c r="H129" s="23" t="s">
+        <v>691</v>
+      </c>
+      <c r="I129" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J129" s="23" t="s">
+        <v>692</v>
+      </c>
+      <c r="K129" s="23" t="s">
+        <v>693</v>
+      </c>
+      <c r="L129" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M129" s="23" t="s">
+        <v>694</v>
+      </c>
+      <c r="N129" s="23" t="s">
         <v>695</v>
       </c>
-      <c r="I129" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J129" s="23" t="s">
+      <c r="O129" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P129" s="25" t="s">
         <v>696</v>
       </c>
-      <c r="K129" s="23" t="s">
+      <c r="Q129" s="25" t="s">
         <v>697</v>
       </c>
-      <c r="L129" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M129" s="23" t="s">
+      <c r="R129" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S129" s="25" t="s">
         <v>698</v>
-      </c>
-      <c r="N129" s="23" t="s">
-        <v>699</v>
-      </c>
-      <c r="O129" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P129" s="25" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q129" s="25" t="s">
-        <v>701</v>
-      </c>
-      <c r="R129" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S129" s="25" t="s">
-        <v>702</v>
       </c>
       <c r="T129" s="25">
         <v>3</v>
@@ -18341,11 +18338,11 @@
       <c r="AA129" s="28"/>
       <c r="AB129" s="25"/>
       <c r="AC129" s="25" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="AD129" s="25"/>
       <c r="AE129" s="23" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="AF129" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18378,40 +18375,40 @@
         <v>137</v>
       </c>
       <c r="H130" s="23" t="s">
+        <v>701</v>
+      </c>
+      <c r="I130" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J130" s="23" t="s">
+        <v>702</v>
+      </c>
+      <c r="K130" s="23" t="s">
+        <v>703</v>
+      </c>
+      <c r="L130" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M130" s="23" t="s">
+        <v>704</v>
+      </c>
+      <c r="N130" s="23" t="s">
         <v>705</v>
       </c>
-      <c r="I130" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J130" s="23" t="s">
+      <c r="O130" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P130" s="25" t="s">
         <v>706</v>
       </c>
-      <c r="K130" s="23" t="s">
+      <c r="Q130" s="25" t="s">
         <v>707</v>
       </c>
-      <c r="L130" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M130" s="23" t="s">
+      <c r="R130" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S130" s="25" t="s">
         <v>708</v>
-      </c>
-      <c r="N130" s="23" t="s">
-        <v>709</v>
-      </c>
-      <c r="O130" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P130" s="25" t="s">
-        <v>710</v>
-      </c>
-      <c r="Q130" s="25" t="s">
-        <v>711</v>
-      </c>
-      <c r="R130" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S130" s="25" t="s">
-        <v>712</v>
       </c>
       <c r="T130" s="25">
         <v>3.4</v>
@@ -18435,11 +18432,11 @@
       <c r="AA130" s="28"/>
       <c r="AB130" s="25"/>
       <c r="AC130" s="25" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="AD130" s="25"/>
       <c r="AE130" s="23" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="AF130" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18472,40 +18469,40 @@
         <v>-180</v>
       </c>
       <c r="H131" s="23" t="s">
+        <v>711</v>
+      </c>
+      <c r="I131" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J131" s="23" t="s">
+        <v>712</v>
+      </c>
+      <c r="K131" s="23" t="s">
+        <v>713</v>
+      </c>
+      <c r="L131" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M131" s="23" t="s">
+        <v>714</v>
+      </c>
+      <c r="N131" s="23" t="s">
         <v>715</v>
       </c>
-      <c r="I131" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J131" s="23" t="s">
+      <c r="O131" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P131" s="25" t="s">
         <v>716</v>
       </c>
-      <c r="K131" s="23" t="s">
+      <c r="Q131" s="25" t="s">
         <v>717</v>
       </c>
-      <c r="L131" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M131" s="23" t="s">
+      <c r="R131" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S131" s="25" t="s">
         <v>718</v>
-      </c>
-      <c r="N131" s="23" t="s">
-        <v>719</v>
-      </c>
-      <c r="O131" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P131" s="25" t="s">
-        <v>720</v>
-      </c>
-      <c r="Q131" s="25" t="s">
-        <v>721</v>
-      </c>
-      <c r="R131" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S131" s="25" t="s">
-        <v>722</v>
       </c>
       <c r="T131" s="25">
         <v>3.5</v>
@@ -18525,11 +18522,11 @@
       <c r="AA131" s="28"/>
       <c r="AB131" s="25"/>
       <c r="AC131" s="25" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="AD131" s="25"/>
       <c r="AE131" s="23" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="AF131" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18562,40 +18559,40 @@
         <v>-172</v>
       </c>
       <c r="H132" s="23" t="s">
+        <v>721</v>
+      </c>
+      <c r="I132" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J132" s="23" t="s">
+        <v>722</v>
+      </c>
+      <c r="K132" s="23" t="s">
+        <v>723</v>
+      </c>
+      <c r="L132" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M132" s="23" t="s">
+        <v>724</v>
+      </c>
+      <c r="N132" s="23" t="s">
         <v>725</v>
       </c>
-      <c r="I132" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J132" s="23" t="s">
+      <c r="O132" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P132" s="25" t="s">
         <v>726</v>
       </c>
-      <c r="K132" s="23" t="s">
+      <c r="Q132" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="L132" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M132" s="23" t="s">
+      <c r="R132" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S132" s="25" t="s">
         <v>728</v>
-      </c>
-      <c r="N132" s="23" t="s">
-        <v>729</v>
-      </c>
-      <c r="O132" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P132" s="25" t="s">
-        <v>730</v>
-      </c>
-      <c r="Q132" s="25" t="s">
-        <v>731</v>
-      </c>
-      <c r="R132" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S132" s="25" t="s">
-        <v>732</v>
       </c>
       <c r="T132" s="25">
         <v>4.2</v>
@@ -18610,7 +18607,7 @@
         <v>4</v>
       </c>
       <c r="X132" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y132" s="26">
         <v>7736</v>
@@ -18622,14 +18619,14 @@
         <v>14.06</v>
       </c>
       <c r="AB132" s="25" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="AC132" s="25" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="AD132" s="25"/>
       <c r="AE132" s="23" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="AF132" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18662,31 +18659,31 @@
         <v>-142</v>
       </c>
       <c r="H133" s="23" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="I133" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J133" s="23" t="s">
+        <v>732</v>
+      </c>
+      <c r="K133" s="23" t="s">
+        <v>733</v>
+      </c>
+      <c r="L133" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M133" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="N133" s="23" t="s">
+        <v>735</v>
+      </c>
+      <c r="O133" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P133" s="25" t="s">
         <v>736</v>
-      </c>
-      <c r="K133" s="23" t="s">
-        <v>737</v>
-      </c>
-      <c r="L133" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M133" s="23" t="s">
-        <v>738</v>
-      </c>
-      <c r="N133" s="23" t="s">
-        <v>739</v>
-      </c>
-      <c r="O133" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P133" s="25" t="s">
-        <v>740</v>
       </c>
       <c r="Q133" s="25"/>
       <c r="R133" s="25"/>
@@ -18702,7 +18699,7 @@
       </c>
       <c r="W133" s="25"/>
       <c r="X133" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y133" s="26">
         <v>7786</v>
@@ -18712,14 +18709,14 @@
         <v>6.37</v>
       </c>
       <c r="AB133" s="25" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="AC133" s="25" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="AD133" s="25"/>
       <c r="AE133" s="23" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="AF133" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18752,40 +18749,40 @@
         <v>1208</v>
       </c>
       <c r="H134" s="23" t="s">
+        <v>740</v>
+      </c>
+      <c r="I134" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J134" s="23" t="s">
+        <v>741</v>
+      </c>
+      <c r="K134" s="23" t="s">
+        <v>742</v>
+      </c>
+      <c r="L134" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M134" s="23" t="s">
+        <v>743</v>
+      </c>
+      <c r="N134" s="23" t="s">
         <v>744</v>
       </c>
-      <c r="I134" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J134" s="23" t="s">
+      <c r="O134" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P134" s="25" t="s">
         <v>745</v>
       </c>
-      <c r="K134" s="23" t="s">
+      <c r="Q134" s="25" t="s">
         <v>746</v>
       </c>
-      <c r="L134" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M134" s="23" t="s">
+      <c r="R134" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S134" s="25" t="s">
         <v>747</v>
-      </c>
-      <c r="N134" s="23" t="s">
-        <v>748</v>
-      </c>
-      <c r="O134" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P134" s="25" t="s">
-        <v>749</v>
-      </c>
-      <c r="Q134" s="25" t="s">
-        <v>750</v>
-      </c>
-      <c r="R134" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S134" s="25" t="s">
-        <v>751</v>
       </c>
       <c r="T134" s="25">
         <v>3.2</v>
@@ -18798,7 +18795,7 @@
       </c>
       <c r="W134" s="25"/>
       <c r="X134" s="26" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="Y134" s="26">
         <v>6518</v>
@@ -18808,14 +18805,14 @@
         <v>13.25</v>
       </c>
       <c r="AB134" s="25" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="AC134" s="25" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="AD134" s="25"/>
       <c r="AE134" s="25" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="AF134" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18848,31 +18845,31 @@
         <v>-180</v>
       </c>
       <c r="H135" s="23" t="s">
+        <v>752</v>
+      </c>
+      <c r="I135" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J135" s="23" t="s">
+        <v>753</v>
+      </c>
+      <c r="K135" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="L135" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M135" s="23" t="s">
+        <v>755</v>
+      </c>
+      <c r="N135" s="23" t="s">
         <v>756</v>
       </c>
-      <c r="I135" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J135" s="23" t="s">
+      <c r="O135" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P135" s="25" t="s">
         <v>757</v>
-      </c>
-      <c r="K135" s="23" t="s">
-        <v>758</v>
-      </c>
-      <c r="L135" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M135" s="23" t="s">
-        <v>759</v>
-      </c>
-      <c r="N135" s="23" t="s">
-        <v>760</v>
-      </c>
-      <c r="O135" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P135" s="25" t="s">
-        <v>761</v>
       </c>
       <c r="Q135" s="25">
         <v>0</v>
@@ -18892,7 +18889,7 @@
         <v>4</v>
       </c>
       <c r="X135" s="25" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="Y135" s="26">
         <v>6429</v>
@@ -18902,14 +18899,14 @@
         <v>25.19</v>
       </c>
       <c r="AB135" s="25" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="AC135" s="25" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="AD135" s="25"/>
       <c r="AE135" s="23" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="AF135" s="25" t="str">
         <f t="shared" si="1"/>
@@ -18942,40 +18939,40 @@
         <v>-225</v>
       </c>
       <c r="H136" s="23" t="s">
+        <v>762</v>
+      </c>
+      <c r="I136" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J136" s="23" t="s">
+        <v>763</v>
+      </c>
+      <c r="K136" s="23" t="s">
+        <v>764</v>
+      </c>
+      <c r="L136" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M136" s="23" t="s">
+        <v>765</v>
+      </c>
+      <c r="N136" s="23" t="s">
         <v>766</v>
       </c>
-      <c r="I136" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J136" s="23" t="s">
+      <c r="O136" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P136" s="25" t="s">
         <v>767</v>
       </c>
-      <c r="K136" s="23" t="s">
+      <c r="Q136" s="25" t="s">
         <v>768</v>
       </c>
-      <c r="L136" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M136" s="23" t="s">
+      <c r="R136" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S136" s="25" t="s">
         <v>769</v>
-      </c>
-      <c r="N136" s="23" t="s">
-        <v>770</v>
-      </c>
-      <c r="O136" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P136" s="25" t="s">
-        <v>771</v>
-      </c>
-      <c r="Q136" s="25" t="s">
-        <v>772</v>
-      </c>
-      <c r="R136" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S136" s="25" t="s">
-        <v>773</v>
       </c>
       <c r="T136" s="25">
         <v>3.5</v>
@@ -19001,11 +18998,11 @@
       </c>
       <c r="AB136" s="25"/>
       <c r="AC136" s="25" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="AD136" s="25"/>
       <c r="AE136" s="23" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="AF136" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19038,40 +19035,40 @@
         <v>-819</v>
       </c>
       <c r="H137" s="23" t="s">
+        <v>772</v>
+      </c>
+      <c r="I137" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J137" s="23" t="s">
+        <v>773</v>
+      </c>
+      <c r="K137" s="23" t="s">
+        <v>774</v>
+      </c>
+      <c r="L137" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M137" s="23" t="s">
+        <v>775</v>
+      </c>
+      <c r="N137" s="23" t="s">
         <v>776</v>
       </c>
-      <c r="I137" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J137" s="23" t="s">
+      <c r="O137" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P137" s="25" t="s">
         <v>777</v>
       </c>
-      <c r="K137" s="23" t="s">
+      <c r="Q137" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="L137" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M137" s="23" t="s">
+      <c r="R137" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S137" s="25" t="s">
         <v>779</v>
-      </c>
-      <c r="N137" s="23" t="s">
-        <v>780</v>
-      </c>
-      <c r="O137" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P137" s="25" t="s">
-        <v>781</v>
-      </c>
-      <c r="Q137" s="25" t="s">
-        <v>782</v>
-      </c>
-      <c r="R137" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S137" s="25" t="s">
-        <v>783</v>
       </c>
       <c r="T137" s="25">
         <v>1.5</v>
@@ -19093,11 +19090,11 @@
       <c r="AA137" s="28"/>
       <c r="AB137" s="25"/>
       <c r="AC137" s="25" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="AD137" s="25"/>
       <c r="AE137" s="23" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="AF137" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19130,40 +19127,40 @@
         <v>-700</v>
       </c>
       <c r="H138" s="23" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="I138" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J138" s="23" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="K138" s="23" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="L138" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M138" s="23" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="N138" s="23">
         <v>0</v>
       </c>
       <c r="O138" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P138" s="25" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="Q138" s="25" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="R138" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S138" s="25" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="T138" s="25">
         <v>2.4</v>
@@ -19187,11 +19184,11 @@
       <c r="AA138" s="28"/>
       <c r="AB138" s="25"/>
       <c r="AC138" s="25" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="AD138" s="25"/>
       <c r="AE138" s="23" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="AF138" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19224,40 +19221,40 @@
         <v>-328</v>
       </c>
       <c r="H139" s="23" t="s">
+        <v>791</v>
+      </c>
+      <c r="I139" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J139" s="23" t="s">
+        <v>792</v>
+      </c>
+      <c r="K139" s="23" t="s">
+        <v>793</v>
+      </c>
+      <c r="L139" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M139" s="23" t="s">
+        <v>794</v>
+      </c>
+      <c r="N139" s="23" t="s">
         <v>795</v>
       </c>
-      <c r="I139" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J139" s="23" t="s">
+      <c r="O139" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P139" s="25" t="s">
         <v>796</v>
       </c>
-      <c r="K139" s="23" t="s">
+      <c r="Q139" s="25" t="s">
         <v>797</v>
       </c>
-      <c r="L139" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M139" s="23" t="s">
+      <c r="R139" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S139" s="25" t="s">
         <v>798</v>
-      </c>
-      <c r="N139" s="23" t="s">
-        <v>799</v>
-      </c>
-      <c r="O139" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P139" s="25" t="s">
-        <v>800</v>
-      </c>
-      <c r="Q139" s="25" t="s">
-        <v>801</v>
-      </c>
-      <c r="R139" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S139" s="25" t="s">
-        <v>802</v>
       </c>
       <c r="T139" s="25">
         <v>2.9</v>
@@ -19279,11 +19276,11 @@
       <c r="AA139" s="28"/>
       <c r="AB139" s="25"/>
       <c r="AC139" s="25" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="AD139" s="25"/>
       <c r="AE139" s="23" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="AF139" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19316,31 +19313,31 @@
         <v>284</v>
       </c>
       <c r="H140" s="23" t="s">
+        <v>801</v>
+      </c>
+      <c r="I140" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J140" s="23" t="s">
+        <v>802</v>
+      </c>
+      <c r="K140" s="23" t="s">
+        <v>803</v>
+      </c>
+      <c r="L140" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M140" s="23" t="s">
+        <v>804</v>
+      </c>
+      <c r="N140" s="23" t="s">
         <v>805</v>
       </c>
-      <c r="I140" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J140" s="23" t="s">
+      <c r="O140" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P140" s="25" t="s">
         <v>806</v>
-      </c>
-      <c r="K140" s="23" t="s">
-        <v>807</v>
-      </c>
-      <c r="L140" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M140" s="23" t="s">
-        <v>808</v>
-      </c>
-      <c r="N140" s="23" t="s">
-        <v>809</v>
-      </c>
-      <c r="O140" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P140" s="25" t="s">
-        <v>810</v>
       </c>
       <c r="Q140" s="25"/>
       <c r="R140" s="25"/>
@@ -19356,7 +19353,7 @@
       </c>
       <c r="W140" s="25"/>
       <c r="X140" s="25" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="Y140" s="26">
         <v>7449</v>
@@ -19367,11 +19364,11 @@
       <c r="AA140" s="28"/>
       <c r="AB140" s="25"/>
       <c r="AC140" s="25" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="AD140" s="25"/>
       <c r="AE140" s="23" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="AF140" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19404,31 +19401,31 @@
         <v>345</v>
       </c>
       <c r="H141" s="23" t="s">
+        <v>810</v>
+      </c>
+      <c r="I141" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J141" s="23" t="s">
+        <v>811</v>
+      </c>
+      <c r="K141" s="23" t="s">
+        <v>812</v>
+      </c>
+      <c r="L141" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M141" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="N141" s="23" t="s">
         <v>814</v>
       </c>
-      <c r="I141" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J141" s="23" t="s">
+      <c r="O141" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P141" s="25" t="s">
         <v>815</v>
-      </c>
-      <c r="K141" s="23" t="s">
-        <v>816</v>
-      </c>
-      <c r="L141" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M141" s="23" t="s">
-        <v>817</v>
-      </c>
-      <c r="N141" s="23" t="s">
-        <v>818</v>
-      </c>
-      <c r="O141" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P141" s="25" t="s">
-        <v>819</v>
       </c>
       <c r="Q141" s="25"/>
       <c r="R141" s="25"/>
@@ -19444,7 +19441,7 @@
       </c>
       <c r="W141" s="25"/>
       <c r="X141" s="25" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="Y141" s="26">
         <v>6629</v>
@@ -19455,7 +19452,7 @@
       <c r="AC141" s="25"/>
       <c r="AD141" s="25"/>
       <c r="AE141" s="23" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="AF141" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19488,40 +19485,40 @@
         <v>337</v>
       </c>
       <c r="H142" s="23" t="s">
+        <v>817</v>
+      </c>
+      <c r="I142" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J142" s="23" t="s">
+        <v>818</v>
+      </c>
+      <c r="K142" s="23" t="s">
+        <v>819</v>
+      </c>
+      <c r="L142" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M142" s="23" t="s">
+        <v>820</v>
+      </c>
+      <c r="N142" s="23" t="s">
         <v>821</v>
       </c>
-      <c r="I142" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J142" s="23" t="s">
+      <c r="O142" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P142" s="25" t="s">
         <v>822</v>
       </c>
-      <c r="K142" s="23" t="s">
+      <c r="Q142" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="L142" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M142" s="23" t="s">
+      <c r="R142" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S142" s="25" t="s">
         <v>824</v>
-      </c>
-      <c r="N142" s="23" t="s">
-        <v>825</v>
-      </c>
-      <c r="O142" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P142" s="25" t="s">
-        <v>826</v>
-      </c>
-      <c r="Q142" s="25" t="s">
-        <v>827</v>
-      </c>
-      <c r="R142" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S142" s="25" t="s">
-        <v>828</v>
       </c>
       <c r="T142" s="25">
         <v>3.5</v>
@@ -19536,7 +19533,7 @@
         <v>2</v>
       </c>
       <c r="X142" s="25" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="Y142" s="26">
         <v>4738</v>
@@ -19549,11 +19546,11 @@
       </c>
       <c r="AB142" s="25"/>
       <c r="AC142" s="25" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="AD142" s="25"/>
       <c r="AE142" s="23" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="AF142" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19586,40 +19583,40 @@
         <v>-248</v>
       </c>
       <c r="H143" s="23" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="I143" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J143" s="23" t="s">
+        <v>827</v>
+      </c>
+      <c r="K143" s="23" t="s">
+        <v>828</v>
+      </c>
+      <c r="L143" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M143" s="23" t="s">
+        <v>829</v>
+      </c>
+      <c r="N143" s="23" t="s">
+        <v>830</v>
+      </c>
+      <c r="O143" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P143" s="25" t="s">
         <v>831</v>
       </c>
-      <c r="K143" s="23" t="s">
+      <c r="Q143" s="25" t="s">
         <v>832</v>
       </c>
-      <c r="L143" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M143" s="23" t="s">
+      <c r="R143" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="S143" s="25" t="s">
         <v>833</v>
-      </c>
-      <c r="N143" s="23" t="s">
-        <v>834</v>
-      </c>
-      <c r="O143" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P143" s="25" t="s">
-        <v>835</v>
-      </c>
-      <c r="Q143" s="25" t="s">
-        <v>836</v>
-      </c>
-      <c r="R143" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="S143" s="25" t="s">
-        <v>837</v>
       </c>
       <c r="T143" s="25">
         <v>3.2</v>
@@ -19643,7 +19640,7 @@
       <c r="AC143" s="25"/>
       <c r="AD143" s="25"/>
       <c r="AE143" s="23" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="AF143" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19676,40 +19673,40 @@
         <v>-127</v>
       </c>
       <c r="H144" s="23" t="s">
+        <v>835</v>
+      </c>
+      <c r="I144" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J144" s="23" t="s">
+        <v>836</v>
+      </c>
+      <c r="K144" s="23" t="s">
+        <v>837</v>
+      </c>
+      <c r="L144" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M144" s="23" t="s">
+        <v>838</v>
+      </c>
+      <c r="N144" s="23" t="s">
         <v>839</v>
       </c>
-      <c r="I144" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J144" s="23" t="s">
+      <c r="O144" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P144" s="25" t="s">
         <v>840</v>
       </c>
-      <c r="K144" s="23" t="s">
+      <c r="Q144" s="25" t="s">
         <v>841</v>
       </c>
-      <c r="L144" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M144" s="23" t="s">
+      <c r="R144" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S144" s="25" t="s">
         <v>842</v>
-      </c>
-      <c r="N144" s="23" t="s">
-        <v>843</v>
-      </c>
-      <c r="O144" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P144" s="25" t="s">
-        <v>844</v>
-      </c>
-      <c r="Q144" s="25" t="s">
-        <v>845</v>
-      </c>
-      <c r="R144" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S144" s="25" t="s">
-        <v>846</v>
       </c>
       <c r="T144" s="25">
         <v>3.7</v>
@@ -19733,11 +19730,11 @@
       <c r="AA144" s="28"/>
       <c r="AB144" s="25"/>
       <c r="AC144" s="25" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="AD144" s="25"/>
       <c r="AE144" s="23" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="AF144" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19770,40 +19767,40 @@
         <v>-129</v>
       </c>
       <c r="H145" s="23" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="I145" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J145" s="23" t="s">
+        <v>845</v>
+      </c>
+      <c r="K145" s="23" t="s">
+        <v>846</v>
+      </c>
+      <c r="L145" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M145" s="23" t="s">
+        <v>847</v>
+      </c>
+      <c r="N145" s="23" t="s">
+        <v>848</v>
+      </c>
+      <c r="O145" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P145" s="25" t="s">
         <v>849</v>
       </c>
-      <c r="K145" s="23" t="s">
+      <c r="Q145" s="25" t="s">
         <v>850</v>
       </c>
-      <c r="L145" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M145" s="23" t="s">
+      <c r="R145" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S145" s="25" t="s">
         <v>851</v>
-      </c>
-      <c r="N145" s="23" t="s">
-        <v>852</v>
-      </c>
-      <c r="O145" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P145" s="25" t="s">
-        <v>853</v>
-      </c>
-      <c r="Q145" s="25" t="s">
-        <v>854</v>
-      </c>
-      <c r="R145" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S145" s="25" t="s">
-        <v>855</v>
       </c>
       <c r="T145" s="25">
         <v>4</v>
@@ -19825,11 +19822,11 @@
       <c r="AA145" s="28"/>
       <c r="AB145" s="25"/>
       <c r="AC145" s="25" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="AD145" s="25"/>
       <c r="AE145" s="23" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="AF145" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19862,40 +19859,40 @@
         <v>149</v>
       </c>
       <c r="H146" s="23" t="s">
+        <v>854</v>
+      </c>
+      <c r="I146" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J146" s="23" t="s">
+        <v>855</v>
+      </c>
+      <c r="K146" s="23" t="s">
+        <v>856</v>
+      </c>
+      <c r="L146" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M146" s="23" t="s">
+        <v>857</v>
+      </c>
+      <c r="N146" s="23" t="s">
         <v>858</v>
       </c>
-      <c r="I146" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J146" s="23" t="s">
+      <c r="O146" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P146" s="25" t="s">
         <v>859</v>
       </c>
-      <c r="K146" s="23" t="s">
+      <c r="Q146" s="25" t="s">
         <v>860</v>
       </c>
-      <c r="L146" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M146" s="23" t="s">
+      <c r="R146" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S146" s="25" t="s">
         <v>861</v>
-      </c>
-      <c r="N146" s="23" t="s">
-        <v>862</v>
-      </c>
-      <c r="O146" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P146" s="25" t="s">
-        <v>863</v>
-      </c>
-      <c r="Q146" s="25" t="s">
-        <v>864</v>
-      </c>
-      <c r="R146" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S146" s="25" t="s">
-        <v>865</v>
       </c>
       <c r="T146" s="25">
         <v>2.9</v>
@@ -19910,7 +19907,7 @@
         <v>2</v>
       </c>
       <c r="X146" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Y146" s="26">
         <v>7183</v>
@@ -19921,11 +19918,11 @@
       <c r="AA146" s="28"/>
       <c r="AB146" s="25"/>
       <c r="AC146" s="25" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="AD146" s="25"/>
       <c r="AE146" s="23" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="AF146" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19958,40 +19955,40 @@
         <v>-95</v>
       </c>
       <c r="H147" s="23" t="s">
+        <v>864</v>
+      </c>
+      <c r="I147" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J147" s="23" t="s">
+        <v>865</v>
+      </c>
+      <c r="K147" s="23" t="s">
+        <v>866</v>
+      </c>
+      <c r="L147" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M147" s="23" t="s">
+        <v>867</v>
+      </c>
+      <c r="N147" s="23" t="s">
         <v>868</v>
       </c>
-      <c r="I147" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J147" s="23" t="s">
+      <c r="O147" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P147" s="25" t="s">
         <v>869</v>
       </c>
-      <c r="K147" s="23" t="s">
+      <c r="Q147" s="25" t="s">
+        <v>768</v>
+      </c>
+      <c r="R147" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S147" s="25" t="s">
         <v>870</v>
-      </c>
-      <c r="L147" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M147" s="23" t="s">
-        <v>871</v>
-      </c>
-      <c r="N147" s="23" t="s">
-        <v>872</v>
-      </c>
-      <c r="O147" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P147" s="25" t="s">
-        <v>873</v>
-      </c>
-      <c r="Q147" s="25" t="s">
-        <v>772</v>
-      </c>
-      <c r="R147" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S147" s="25" t="s">
-        <v>874</v>
       </c>
       <c r="T147" s="25">
         <v>3.5</v>
@@ -20011,11 +20008,11 @@
       <c r="AA147" s="28"/>
       <c r="AB147" s="25"/>
       <c r="AC147" s="25" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="AD147" s="25"/>
       <c r="AE147" s="23" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="AF147" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20049,37 +20046,37 @@
       </c>
       <c r="H148" s="23"/>
       <c r="I148" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J148" s="23" t="s">
+        <v>873</v>
+      </c>
+      <c r="K148" s="23" t="s">
+        <v>874</v>
+      </c>
+      <c r="L148" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="M148" s="25" t="s">
+        <v>875</v>
+      </c>
+      <c r="N148" s="23" t="s">
+        <v>876</v>
+      </c>
+      <c r="O148" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P148" s="25" t="s">
         <v>877</v>
-      </c>
-      <c r="K148" s="23" t="s">
-        <v>878</v>
-      </c>
-      <c r="L148" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="M148" s="25" t="s">
-        <v>879</v>
-      </c>
-      <c r="N148" s="23" t="s">
-        <v>880</v>
-      </c>
-      <c r="O148" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P148" s="25" t="s">
-        <v>881</v>
       </c>
       <c r="Q148" s="25">
         <v>1</v>
       </c>
       <c r="R148" s="25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S148" s="25" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="T148" s="25">
         <v>3.4</v>
@@ -20092,7 +20089,7 @@
         <v>4</v>
       </c>
       <c r="X148" s="25" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="Y148" s="26">
         <v>6500</v>
@@ -20103,11 +20100,11 @@
       <c r="AA148" s="28"/>
       <c r="AB148" s="25"/>
       <c r="AC148" s="25" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="AD148" s="25"/>
       <c r="AE148" s="23" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="AF148" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20140,40 +20137,40 @@
         <v>-116</v>
       </c>
       <c r="H149" s="23" t="s">
+        <v>882</v>
+      </c>
+      <c r="I149" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J149" s="23" t="s">
+        <v>883</v>
+      </c>
+      <c r="K149" s="23" t="s">
+        <v>884</v>
+      </c>
+      <c r="L149" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M149" s="23" t="s">
+        <v>885</v>
+      </c>
+      <c r="N149" s="23" t="s">
         <v>886</v>
       </c>
-      <c r="I149" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J149" s="23" t="s">
+      <c r="O149" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P149" s="25" t="s">
         <v>887</v>
       </c>
-      <c r="K149" s="23" t="s">
+      <c r="Q149" s="25" t="s">
         <v>888</v>
       </c>
-      <c r="L149" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M149" s="23" t="s">
+      <c r="R149" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S149" s="25" t="s">
         <v>889</v>
-      </c>
-      <c r="N149" s="23" t="s">
-        <v>890</v>
-      </c>
-      <c r="O149" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P149" s="25" t="s">
-        <v>891</v>
-      </c>
-      <c r="Q149" s="25" t="s">
-        <v>892</v>
-      </c>
-      <c r="R149" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S149" s="25" t="s">
-        <v>893</v>
       </c>
       <c r="T149" s="25">
         <v>2.6</v>
@@ -20195,7 +20192,7 @@
       </c>
       <c r="AB149" s="45"/>
       <c r="AC149" s="25" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="AD149" s="45"/>
       <c r="AE149" s="23"/>
@@ -20230,40 +20227,40 @@
         <v>345</v>
       </c>
       <c r="H150" s="23" t="s">
+        <v>891</v>
+      </c>
+      <c r="I150" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J150" s="23" t="s">
+        <v>892</v>
+      </c>
+      <c r="K150" s="23" t="s">
+        <v>893</v>
+      </c>
+      <c r="L150" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M150" s="23" t="s">
+        <v>894</v>
+      </c>
+      <c r="N150" s="23" t="s">
         <v>895</v>
       </c>
-      <c r="I150" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J150" s="23" t="s">
+      <c r="O150" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P150" s="25" t="s">
         <v>896</v>
       </c>
-      <c r="K150" s="23" t="s">
+      <c r="Q150" s="25" t="s">
         <v>897</v>
       </c>
-      <c r="L150" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M150" s="23" t="s">
+      <c r="R150" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S150" s="25" t="s">
         <v>898</v>
-      </c>
-      <c r="N150" s="23" t="s">
-        <v>899</v>
-      </c>
-      <c r="O150" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P150" s="25" t="s">
-        <v>900</v>
-      </c>
-      <c r="Q150" s="25" t="s">
-        <v>901</v>
-      </c>
-      <c r="R150" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S150" s="25" t="s">
-        <v>902</v>
       </c>
       <c r="T150" s="25">
         <v>2.5</v>
@@ -20287,11 +20284,11 @@
       <c r="AA150" s="28"/>
       <c r="AB150" s="45"/>
       <c r="AC150" s="25" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="AD150" s="45"/>
       <c r="AE150" s="25" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="AF150" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20324,40 +20321,40 @@
         <v>-313</v>
       </c>
       <c r="H151" s="23" t="s">
+        <v>901</v>
+      </c>
+      <c r="I151" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J151" s="23" t="s">
+        <v>902</v>
+      </c>
+      <c r="K151" s="23" t="s">
+        <v>903</v>
+      </c>
+      <c r="L151" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M151" s="23" t="s">
+        <v>904</v>
+      </c>
+      <c r="N151" s="23" t="s">
         <v>905</v>
       </c>
-      <c r="I151" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J151" s="23" t="s">
+      <c r="O151" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P151" s="25" t="s">
         <v>906</v>
       </c>
-      <c r="K151" s="23" t="s">
+      <c r="Q151" s="25" t="s">
         <v>907</v>
       </c>
-      <c r="L151" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M151" s="23" t="s">
+      <c r="R151" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S151" s="25" t="s">
         <v>908</v>
-      </c>
-      <c r="N151" s="23" t="s">
-        <v>909</v>
-      </c>
-      <c r="O151" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P151" s="25" t="s">
-        <v>910</v>
-      </c>
-      <c r="Q151" s="25" t="s">
-        <v>911</v>
-      </c>
-      <c r="R151" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S151" s="25" t="s">
-        <v>912</v>
       </c>
       <c r="T151" s="25">
         <v>4</v>
@@ -20381,7 +20378,7 @@
       <c r="AC151" s="25"/>
       <c r="AD151" s="25"/>
       <c r="AE151" s="25" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="AF151" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20411,40 +20408,40 @@
       </c>
       <c r="G152" s="21"/>
       <c r="H152" s="23" t="s">
+        <v>910</v>
+      </c>
+      <c r="I152" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J152" s="23" t="s">
+        <v>911</v>
+      </c>
+      <c r="K152" s="23" t="s">
+        <v>912</v>
+      </c>
+      <c r="L152" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M152" s="23" t="s">
+        <v>913</v>
+      </c>
+      <c r="N152" s="23" t="s">
         <v>914</v>
       </c>
-      <c r="I152" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J152" s="23" t="s">
+      <c r="O152" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="P152" s="25" t="s">
         <v>915</v>
       </c>
-      <c r="K152" s="23" t="s">
+      <c r="Q152" s="25" t="s">
         <v>916</v>
       </c>
-      <c r="L152" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M152" s="23" t="s">
+      <c r="R152" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S152" s="25" t="s">
         <v>917</v>
-      </c>
-      <c r="N152" s="23" t="s">
-        <v>918</v>
-      </c>
-      <c r="O152" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P152" s="25" t="s">
-        <v>919</v>
-      </c>
-      <c r="Q152" s="25" t="s">
-        <v>920</v>
-      </c>
-      <c r="R152" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S152" s="25" t="s">
-        <v>921</v>
       </c>
       <c r="T152" s="25">
         <v>3</v>
@@ -20459,7 +20456,7 @@
         <v>1</v>
       </c>
       <c r="X152" s="25" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="Y152" s="26">
         <v>6773</v>
@@ -20467,11 +20464,11 @@
       <c r="Z152" s="27"/>
       <c r="AA152" s="28"/>
       <c r="AC152" s="25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AD152" s="25"/>
       <c r="AE152" s="25" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="AF152" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20487,7 +20484,7 @@
       <c r="B153" s="30">
         <v>69.900000000000006</v>
       </c>
-      <c r="C153" s="49">
+      <c r="C153" s="25">
         <v>13.6</v>
       </c>
       <c r="D153" s="30">
@@ -20501,40 +20498,40 @@
       </c>
       <c r="G153" s="21"/>
       <c r="H153" s="23" t="s">
+        <v>919</v>
+      </c>
+      <c r="I153" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J153" s="23" t="s">
+        <v>782</v>
+      </c>
+      <c r="K153" s="23" t="s">
+        <v>912</v>
+      </c>
+      <c r="L153" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M153" s="23" t="s">
+        <v>920</v>
+      </c>
+      <c r="N153" s="23" t="s">
+        <v>921</v>
+      </c>
+      <c r="O153" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="P153" s="25" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q153" s="25" t="s">
         <v>923</v>
       </c>
-      <c r="I153" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J153" s="23" t="s">
-        <v>786</v>
-      </c>
-      <c r="K153" s="23" t="s">
-        <v>916</v>
-      </c>
-      <c r="L153" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M153" s="23" t="s">
+      <c r="R153" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S153" s="25" t="s">
         <v>924</v>
-      </c>
-      <c r="N153" s="23" t="s">
-        <v>925</v>
-      </c>
-      <c r="O153" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="P153" s="25" t="s">
-        <v>926</v>
-      </c>
-      <c r="Q153" s="25" t="s">
-        <v>927</v>
-      </c>
-      <c r="R153" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S153" s="25" t="s">
-        <v>928</v>
       </c>
       <c r="T153" s="25">
         <v>3.2</v>
@@ -20557,14 +20554,14 @@
       </c>
       <c r="AA153" s="28"/>
       <c r="AB153" s="25" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="AC153" s="25" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="AD153" s="25"/>
       <c r="AE153" s="23" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="AF153" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20580,7 +20577,7 @@
       <c r="B154" s="30">
         <v>70.45</v>
       </c>
-      <c r="C154" s="49">
+      <c r="C154" s="25">
         <v>13.9</v>
       </c>
       <c r="D154" s="30">
@@ -20594,40 +20591,40 @@
       </c>
       <c r="G154" s="21"/>
       <c r="H154" s="23" t="s">
+        <v>928</v>
+      </c>
+      <c r="I154" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="J154" s="23" t="s">
+        <v>929</v>
+      </c>
+      <c r="K154" s="23" t="s">
+        <v>930</v>
+      </c>
+      <c r="L154" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M154" s="23" t="s">
+        <v>931</v>
+      </c>
+      <c r="N154" s="23" t="s">
         <v>932</v>
       </c>
-      <c r="I154" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="J154" s="23" t="s">
+      <c r="O154" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P154" s="25" t="s">
         <v>933</v>
       </c>
-      <c r="K154" s="23" t="s">
+      <c r="Q154" s="25" t="s">
         <v>934</v>
       </c>
-      <c r="L154" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="M154" s="23" t="s">
+      <c r="R154" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="S154" s="25" t="s">
         <v>935</v>
-      </c>
-      <c r="N154" s="23" t="s">
-        <v>936</v>
-      </c>
-      <c r="O154" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P154" s="25" t="s">
-        <v>937</v>
-      </c>
-      <c r="Q154" s="25" t="s">
-        <v>938</v>
-      </c>
-      <c r="R154" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S154" s="25" t="s">
-        <v>939</v>
       </c>
       <c r="T154" s="25">
         <v>2</v>
@@ -20653,7 +20650,7 @@
       <c r="AC154" s="25"/>
       <c r="AD154" s="25"/>
       <c r="AE154" s="23" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="AF154" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20669,7 +20666,7 @@
       <c r="B155" s="30">
         <v>69.7</v>
       </c>
-      <c r="C155" s="49">
+      <c r="C155" s="25">
         <v>13.4</v>
       </c>
       <c r="D155" s="30">
@@ -20686,40 +20683,40 @@
         <v>132</v>
       </c>
       <c r="H155" s="23" t="s">
+        <v>937</v>
+      </c>
+      <c r="I155" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J155" s="23" t="s">
+        <v>938</v>
+      </c>
+      <c r="K155" s="23" t="s">
+        <v>939</v>
+      </c>
+      <c r="L155" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M155" s="23" t="s">
+        <v>940</v>
+      </c>
+      <c r="N155" s="23" t="s">
         <v>941</v>
       </c>
-      <c r="I155" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="J155" s="23" t="s">
+      <c r="O155" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P155" s="25" t="s">
         <v>942</v>
       </c>
-      <c r="K155" s="23" t="s">
+      <c r="Q155" s="25" t="s">
         <v>943</v>
       </c>
-      <c r="L155" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="M155" s="23" t="s">
+      <c r="R155" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="S155" s="25" t="s">
         <v>944</v>
-      </c>
-      <c r="N155" s="23" t="s">
-        <v>945</v>
-      </c>
-      <c r="O155" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P155" s="25" t="s">
-        <v>946</v>
-      </c>
-      <c r="Q155" s="25" t="s">
-        <v>947</v>
-      </c>
-      <c r="R155" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="S155" s="25" t="s">
-        <v>948</v>
       </c>
       <c r="T155" s="25">
         <v>2.5</v>
@@ -20734,7 +20731,7 @@
         <v>2</v>
       </c>
       <c r="X155" s="25" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="Y155" s="26">
         <v>4500</v>
@@ -20745,7 +20742,7 @@
       <c r="AC155" s="25"/>
       <c r="AD155" s="25"/>
       <c r="AE155" s="23" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="AF155" s="25" t="str">
         <f t="shared" si="1"/>
@@ -20759,7 +20756,7 @@
         <v>46236</v>
       </c>
       <c r="B156" s="30"/>
-      <c r="C156" s="49"/>
+      <c r="C156" s="25"/>
       <c r="D156" s="30"/>
       <c r="E156" s="26"/>
       <c r="F156" s="27"/>
